--- a/ORTIZNOR_Tabla_Maestra.xlsx
+++ b/ORTIZNOR_Tabla_Maestra.xlsx
@@ -18,8 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referencias" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diccionario Maestro'!$A$1:$G$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reglas de Redacción'!$A$1:$B$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diccionario Maestro'!$A$1:$G$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reglas de Redacción'!$A$1:$B$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reglas Clínicas'!$A$1:$C$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -783,22 +783,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Cavidades izquierdas</t>
+          <t>Datos generales / Apertura</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VI / VI↑ / VI DIL</t>
+          <t>"317 Nombre" (cama y nombre juntos)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ventrículo izquierdo dilatado</t>
+          <t>Tolerancia de entrada</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ventrículo izquierdo con diámetros aumentados, de morfología esferiforme</t>
+          <t>Si la cama/AMB y el nombre se escriben en la misma línea separados por espacio, el sistema los separa automáticamente</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Evita error si en el celular se escriben sin salto de línea entre cama y nombre</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>ASE 2015</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -825,27 +825,27 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>HVI</t>
+          <t>VI / VI↑ / VI DIL</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Hipertrofia ventricular izquierda</t>
+          <t>Ventrículo izquierdo dilatado</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Ventrículo izquierdo con hipertrofia de sus paredes, con diámetros adecuados</t>
+          <t>Ventrículo izquierdo con diámetros aumentados, de morfología esferiforme</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Según masa indexada</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Automático si masa/índice supera límite normal (según sexo)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -862,32 +862,32 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>LHVI / Leve HVI</t>
+          <t>## / ## (en la posición de VI diástole de la secuencia fija)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Hipertrofia leve</t>
+          <t>Diámetro diastólico / sistólico del VI combinados en una sola línea</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Ventrículo izquierdo con leve hipertrofia de sus paredes</t>
+          <t>Se separan automáticamente: primer valor = VI diástole, segundo valor = VI sístole (mm → cm)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Formato alternativo a escribir el diámetro diastólico solo (deja sístole en blanco); ocupa la 6ª posición de las 7 medidas fijas</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>ASE 2015</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -899,32 +899,32 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Septum</t>
+          <t>HVI</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Hipertrofia septal leve</t>
+          <t>Hipertrofia ventricular izquierda</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Leve hipertrofia del septum interventricular</t>
+          <t>Ventrículo izquierdo con hipertrofia de sus paredes, con diámetros adecuados</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>Según masa indexada</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Excluyente con Espolón</t>
+          <t>Automático si masa/índice supera límite normal (según sexo)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE 2015</t>
         </is>
       </c>
     </row>
@@ -936,32 +936,32 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Septum↑ / Sept↑</t>
+          <t>LHVI / Leve HVI</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fibrosis septal</t>
+          <t>Hipertrofia leve</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Septum interventricular con aumento de densidad acústica</t>
+          <t>Ventrículo izquierdo con leve hipertrofia de sus paredes</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Leve</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Reemplazo de músculo por colágeno; se integra en cardiopatía isquémica. Excluyente con Espolón</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE 2015</t>
         </is>
       </c>
     </row>
@@ -973,27 +973,27 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Septum↓ / Sept↓</t>
+          <t>Septum</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Adelgazamiento septal</t>
+          <t>Hipertrofia septal leve</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Septum interventricular adelgazado</t>
+          <t>Leve hipertrofia del septum interventricular</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Leve</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Se integra en cardiopatía isquémica. Excluyente con Espolón</t>
+          <t>Excluyente con Espolón</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Septum↑↓ / Sept↑↓</t>
+          <t>Septum↑ / Sept↑</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fibrosis + adelgazamiento septal</t>
+          <t>Fibrosis septal</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Septum interventricular con aumento de densidad acústica y adelgazado</t>
+          <t>Septum interventricular con aumento de densidad acústica</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Se integra en cardiopatía isquémica. Excluyente con Espolón</t>
+          <t>Reemplazo de músculo por colágeno; se integra en cardiopatía isquémica. Excluyente con Espolón</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1047,17 +1047,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Espolón</t>
+          <t>Septum↓ / Sept↓</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Engrosamiento miocárdico septal basal</t>
+          <t>Adelgazamiento septal</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Engrosamiento miocárdico septal basal</t>
+          <t>Septum interventricular adelgazado</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>No concluye automáticamente. Excluyente con familia Septum↑/↓</t>
+          <t>Se integra en cardiopatía isquémica. Excluyente con Espolón</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,27 +1084,27 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>AN VI ##</t>
+          <t>Septum↑↓ / Sept↑↓</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Aneurisma apical del VI</t>
+          <t>Fibrosis + adelgazamiento septal</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Aneurisma apical del ventrículo izquierdo de ## cm</t>
+          <t>Septum interventricular con aumento de densidad acústica y adelgazado</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Según tamaño</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Se integra con cardiopatía isquémica, trombo o alteración segmentaria</t>
+          <t>Se integra en cardiopatía isquémica. Excluyente con Espolón</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cuerda</t>
+          <t>Espolón</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Falsa cuerda tendinosa</t>
+          <t>Engrosamiento miocárdico septal basal</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Presencia de falsa cuerda tendinosa intraventricular izquierda (puede especificarse ubicación, ej. lateroseptal apical)</t>
+          <t>Engrosamiento miocárdico septal basal</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>No concluye</t>
+          <t>No concluye automáticamente. Excluyente con familia Septum↑/↓</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1158,27 +1158,27 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>AI ≤20 cm²</t>
+          <t>AN VI ##</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Aurícula izquierda normal</t>
+          <t>Aneurisma apical del VI</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>"Aurícula izquierda de tamaño y forma normal."</t>
+          <t>Aneurisma apical del ventrículo izquierdo de ## cm</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Normal (≤20 cm² inclusive)</t>
+          <t>Según tamaño</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>No se menciona en conclusiones. Si el área es exactamente 20 cm², se usa el diámetro de AI (2º valor de la secuencia fija de medidas) como desempate: diámetro &gt;4.0 cm → se reclasifica como dilatada</t>
+          <t>Se integra con cardiopatía isquémica, trombo o alteración segmentaria</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>AI 20–40 cm² (con diámetro &gt;4.0 cm si área=20) / AI↑</t>
+          <t>Cuerda</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Aurícula izquierda dilatada</t>
+          <t>Falsa cuerda tendinosa</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>"Aurícula izquierda dilatada, con área de xx cm²."</t>
+          <t>Presencia de falsa cuerda tendinosa intraventricular izquierda (puede especificarse ubicación, ej. lateroseptal apical)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Dilatada (binario)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Conclusión independiente si aislada; se integra con IM/SM/FA/DD si coexisten</t>
+          <t>No concluye</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1232,27 +1232,27 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>AI &gt;40 cm²</t>
+          <t>AI ≤20 cm²</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Aurícula izquierda severamente dilatada</t>
+          <t>Aurícula izquierda normal</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>"Aurícula izquierda severamente dilatada, con área de xx cm²."</t>
+          <t>"Aurícula izquierda de tamaño y forma normal."</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Severa (mención especial)</t>
+          <t>Normal (≤20 cm² inclusive)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Se integra igual que dilatada, con calificativo "severa"</t>
+          <t>No se menciona en conclusiones. Si el área es exactamente 20 cm², se usa el diámetro de AI (2º valor de la secuencia fija de medidas) como desempate: diámetro &gt;4.0 cm → se reclasifica como dilatada</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1269,27 +1269,27 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>AI ##/##</t>
+          <t>AI 20–40 cm² (con diámetro &gt;4.0 cm si área=20) / AI↑</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Área / Volumen total de AI (ml, sin indexar)</t>
+          <t>Aurícula izquierda dilatada</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>"...con área de xx cm² y volumen de xx ml (Volumen AI xx ml/m²)."</t>
+          <t>"Aurícula izquierda dilatada, con área de xx cm²."</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Según área</t>
+          <t>Dilatada (binario)</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Si hay peso/talla, se calcula y agrega automáticamente el Volumen AI indexado (ml/m²)</t>
+          <t>Conclusión independiente si aislada; se integra con IM/SM/FA/DD si coexisten</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1306,64 +1306,64 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>AI área4C*área2C*longitud</t>
+          <t>AI &gt;40 cm²</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Cálculo automático de volumen AI</t>
+          <t>Aurícula izquierda severamente dilatada</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Calcula volumen total y Volumen AI indexado (ml/m²) usando peso/talla/SC</t>
+          <t>"Aurícula izquierda severamente dilatada, con área de xx cm²."</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Severa (mención especial)</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Se integra igual que dilatada, con calificativo "severa"</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>ASE 2015</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Cavidades derechas</t>
+          <t>Cavidades izquierdas</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>AD (normal / dilatada)</t>
+          <t>AI ##/##</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Aurícula derecha</t>
+          <t>Área / Volumen total de AI (ml, sin indexar)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Se describe siempre: "Aurícula derecha de tamaño y forma normal" o "Aurícula derecha dilatada, con área de xx cm²"</t>
+          <t>"...con área de xx cm² y volumen de xx ml (Volumen AI xx ml/m²)."</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Binario (corte pendiente de definir con precisión numérica)</t>
+          <t>Según área</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Igual patrón que AI: se integra si coexiste con otros hallazgos</t>
+          <t>Si hay peso/talla, se calcula y agrega automáticamente el Volumen AI indexado (ml/m²)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1375,37 +1375,37 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Cavidades derechas</t>
+          <t>Cavidades izquierdas</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>AD↓ ##%</t>
+          <t>AI área4C*área2C*longitud</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Colapso de AD</t>
+          <t>Cálculo automático de volumen AI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Colapso del área auricular derecha de ##%</t>
+          <t>Calcula volumen total y Volumen AI indexado (ml/m²) usando peso/talla/SC</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Según %</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>No concluye solo; se integra únicamente con derrame pericárdico (compromiso hemodinámico)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE 2015</t>
         </is>
       </c>
     </row>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>DER DIL / D↑</t>
+          <t>AD (normal / dilatada)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Cavidades derechas dilatadas</t>
+          <t>Aurícula derecha</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Cavidades derechas dilatadas</t>
+          <t>Se describe siempre: "Aurícula derecha de tamaño y forma normal" o "Aurícula derecha dilatada, con área de xx cm²"</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Binario (corte pendiente de definir con precisión numérica)</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Se integra con hipertensión pulmonar</t>
+          <t>Igual patrón que AI: se integra si coexiste con otros hallazgos</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1454,27 +1454,27 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Apex bi</t>
+          <t>AD↓ ##%</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VD comparte el ápex</t>
+          <t>Colapso de AD</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Cavidades derechas dilatadas, con VD que se extiende hasta compartir el ápex con el VI</t>
+          <t>Colapso del área auricular derecha de ##%</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Según %</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Implica dilatación del VD; debe reflejarse en conclusiones</t>
+          <t>No concluye solo; se integra únicamente con derrame pericárdico (compromiso hemodinámico)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1491,17 +1491,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Ápex der</t>
+          <t>DER DIL / D↑</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Ápex ocupado por VD</t>
+          <t>Cavidades derechas dilatadas</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Dilatación de cavidades derechas con ápex cardíaco ocupado por el VD</t>
+          <t>Cavidades derechas dilatadas</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Debe reflejarse en conclusiones</t>
+          <t>Se integra con hipertensión pulmonar</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1528,32 +1528,32 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>VD ##</t>
+          <t>Apex bi</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Grosor de pared libre del VD</t>
+          <t>VD comparte el ápex</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Pared libre del ventrículo derecho de xx cm (medido en mm, descrito en cm)</t>
+          <t>Cavidades derechas dilatadas, con VD que se extiende hasta compartir el ápex con el VI</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Anormal si &gt;0.5 cm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Implica dilatación del VD; debe reflejarse en conclusiones</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>ASE 2015</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>D ##</t>
+          <t>Ápex der</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Diámetro del RVOT (eje corto paraesternal)</t>
+          <t>Ápex ocupado por VD</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Tracto de salida del ventrículo derecho con diámetro de xx cm (medido en mm, descrito en cm)</t>
+          <t>Dilatación de cavidades derechas con ápex cardíaco ocupado por el VD</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Dilatado si &gt;30 mm (3.0 cm)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Se integra con D↑/AD↑/hipertensión pulmonar si coexiste</t>
+          <t>Debe reflejarse en conclusiones</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR / ASE</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -1602,32 +1602,32 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CV ## / CAVA ##</t>
+          <t>VD ##</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Vena cava inferior, colapso adecuado</t>
+          <t>Grosor de pared libre del VD</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>"Vena cava inferior de xx mm (xx cm), que colapsa adecuadamente con la respiración."</t>
+          <t>Pared libre del ventrículo derecho de xx cm (medido en mm, descrito en cm)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Anormal si &gt;0.5 cm</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>CV normal + colapso adecuado → presión de AD normal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE 2015</t>
         </is>
       </c>
     </row>
@@ -1639,64 +1639,64 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>CV ##↓ / CAVA ##↓</t>
+          <t>D ##</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Vena cava inferior, colapso inadecuado</t>
+          <t>Diámetro del RVOT (eje corto paraesternal)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>"Vena cava inferior de xx mm (xx cm), que no colapsa adecuadamente con la respiración."</t>
+          <t>Tracto de salida del ventrículo derecho con diámetro de xx cm (medido en mm, descrito en cm)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Anormal</t>
+          <t>Dilatado si &gt;30 mm (3.0 cm)</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Sugiere presión de AD elevada</t>
+          <t>Se integra con D↑/AD↑/hipertensión pulmonar si coexiste</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ORTIZNOR / ASE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Tabiques</t>
+          <t>Cavidades derechas</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>CV ## / CAVA ##</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Comunicación interauricular</t>
+          <t>Vena cava inferior, colapso adecuado</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Solución de continuidad en tercio medio del tabique de xx cm</t>
+          <t>"Vena cava inferior de xx mm (xx cm), que colapsa adecuadamente con la respiración."</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Tipos: ostium secundum (defecto), ostium primum, seno venoso. QP/QS si existe, obligatorio en conclusión</t>
+          <t>CV normal + colapso adecuado → presión de AD normal</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1708,32 +1708,32 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Tabiques</t>
+          <t>Cavidades derechas</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>CV ##↓ / CAVA ##↓</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Comunicación interventricular</t>
+          <t>Vena cava inferior, colapso inadecuado</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Solución de continuidad en tabique interventricular</t>
+          <t>"Vena cava inferior de xx mm (xx cm), que no colapsa adecuadamente con la respiración."</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Anormal</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tipos: perimembranosa (defecto), muscular, subaórtica</t>
+          <t>Sugiere presión de AD elevada</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1750,17 +1750,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>FOP ##x##</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Foramen oval permeable (confirmado)</t>
+          <t>Comunicación interauricular</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Túnel de xx cm de longitud y xx cm de diámetro</t>
+          <t>Solución de continuidad en tercio medio del tabique de xx cm</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Foramen oval permeable, con cortocircuito interauricular." No confundir con CIA</t>
+          <t>Tipos: ostium secundum (defecto), ostium primum, seno venoso. QP/QS si existe, obligatorio en conclusión</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1787,27 +1787,27 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>FOP?</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Foramen oval permeable dudoso</t>
+          <t>Comunicación interventricular</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Hallazgo no concluyente (ventana subóptima u otra causa)</t>
+          <t>Solución de continuidad en tabique interventricular</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Dudoso</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Sugestivo de foramen oval permeable." Sin recomendar estudio adicional</t>
+          <t>Tipos: perimembranosa (defecto), muscular, subaórtica</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>AN ##x##</t>
+          <t>FOP ##x##</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Aneurisma del septum interauricular</t>
+          <t>Foramen oval permeable (confirmado)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Base de xx cm y desplazamiento de xx cm, sin evidencia de solución de continuidad</t>
+          <t>Túnel de xx cm de longitud y xx cm de diámetro</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Aneurisma del septum interauricular, sin evidencia de cortocircuito." Si coexiste FOP, ambos se describen y FOP aporta el cortocircuito</t>
+          <t>Conclusión: "Foramen oval permeable, con cortocircuito interauricular." No confundir con CIA</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1861,27 +1861,27 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>S/S</t>
+          <t>FOP?</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Sobrecarga septal sistólica</t>
+          <t>Foramen oval permeable dudoso</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Rectificación septal en sístole</t>
+          <t>Hallazgo no concluyente (ventana subóptima u otra causa)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Dudoso</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Típica de sobrecarga de presión (HP). Nunca concluye sola; se integra con hipertensión pulmonar</t>
+          <t>Conclusión: "Sugestivo de foramen oval permeable." Sin recomendar estudio adicional</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>S/D</t>
+          <t>AN ##x##</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Sobrecarga septal diastólica</t>
+          <t>Aneurisma del septum interauricular</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Rectificación septal en diástole</t>
+          <t>Base de xx cm y desplazamiento de xx cm, sin evidencia de solución de continuidad</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Típica de sobrecarga de volumen (CIA, IT severa). Nunca concluye sola</t>
+          <t>Conclusión: "Aneurisma del septum interauricular, sin evidencia de cortocircuito." Si coexiste FOP, ambos se describen y FOP aporta el cortocircuito</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>S/SD</t>
+          <t>S/S</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Sobrecarga septal combinada</t>
+          <t>Sobrecarga septal sistólica</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Rectificación septal en sístole y diástole</t>
+          <t>Rectificación septal en sístole</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Sobrecarga mixta presión/volumen. Nunca concluye sola</t>
+          <t>Típica de sobrecarga de presión (HP). Nunca concluye sola; se integra con hipertensión pulmonar</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1967,22 +1967,22 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Pericardio</t>
+          <t>Tabiques</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>PERIC (solo)</t>
+          <t>S/D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Engrosamiento pericárdico genérico</t>
+          <t>Sobrecarga septal diastólica</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>"Halo de ausencia de ecos asociado a engrosamiento y realce de hojas pericárdicas."</t>
+          <t>Rectificación septal en diástole</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Inflamación pericárdica." Solo si PERIC fue dictado explícitamente</t>
+          <t>Típica de sobrecarga de volumen (CIA, IT severa). Nunca concluye sola</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2004,32 +2004,32 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Pericardio</t>
+          <t>Tabiques</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DP &lt;80 / DPP &lt;80</t>
+          <t>S/SD</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Espesor del halo (cm)</t>
+          <t>Sobrecarga septal combinada</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>"...con separación de hojas pericárdicas de xx cm..."</t>
+          <t>Rectificación septal en sístole y diástole</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Espesor en cm</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Sin PERIC: conclusión solo "Derrame pericárdico" (sin calificar de inflamatorio)</t>
+          <t>Sobrecarga mixta presión/volumen. Nunca concluye sola</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>DP ≥80 / DPP ≥80</t>
+          <t>PERIC (solo)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Volumen estimado del derrame (cc)</t>
+          <t>Engrosamiento pericárdico genérico</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>"...con volumen estimado de xx cc..."</t>
+          <t>"Halo de ausencia de ecos asociado a engrosamiento y realce de hojas pericárdicas."</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Volumen en cc</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Igual regla: inflamatorio solo si PERIC fue dictado</t>
+          <t>Conclusión: "Inflamación pericárdica." Solo si PERIC fue dictado explícitamente</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2083,27 +2083,27 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>DP + DPP juntos</t>
+          <t>DP &lt;80 / DPP &lt;80</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Derrame circunferencial</t>
+          <t>Espesor del halo (cm)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Describe espesor/volumen anterior y posterior combinados</t>
+          <t>"...con separación de hojas pericárdicas de xx cm..."</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Espesor en cm</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Conclusión menciona "circunferencial"</t>
+          <t>Sin PERIC: conclusión solo "Derrame pericárdico" (sin calificar de inflamatorio)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2120,27 +2120,27 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>M ##% / T ##%</t>
+          <t>DP ≥80 / DPP ≥80</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Variación respiratoria mitral/tricuspídea</t>
+          <t>Volumen estimado del derrame (cc)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Variación respiratoria del flujo de ##%</t>
+          <t>Volumen estimado del derrame en cc</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Significativa si ≥25%</t>
+          <t>Leve ≤150 cc; Moderado 151–300 cc; Severo &gt;300 cc</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Se integra en compromiso hemodinámico solo si hay derrame (DP/DPP)</t>
+          <t>Conclusión incluye severidad y volumen: "DERRAME PERICARDICO [LEVE/MODERADO/SEVERO], CON VOLUMEN ESTIMADO DE ## CC."</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2157,27 +2157,27 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AD↓ + M/T ≥25% + DP</t>
+          <t>DP + DPP juntos</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Compromiso hemodinámico</t>
+          <t>Derrame circunferencial</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Describe espesor/volumen anterior y posterior combinados</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>"Derrame pericárdico con signos de aumento de presión intrapericárdica y compromiso hemodinámico" (+ "Inflamación" si PERIC presente)</t>
+          <t>Conclusión menciona "circunferencial"</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2189,32 +2189,32 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Contractilidad</t>
+          <t>Pericardio</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>M ##% / T ##%</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Aquinesia</t>
+          <t>Variación respiratoria mitral/tricuspídea</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Ausencia de movimiento del segmento indicado</t>
+          <t>Variación respiratoria del flujo de ##%</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Severa</t>
+          <t>Significativa si ≥25%</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>No implica obligatoriamente infarto antiguo</t>
+          <t>Se integra en compromiso hemodinámico solo si hay derrame (DP/DPP)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2226,32 +2226,32 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Contractilidad</t>
+          <t>Pericardio</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>HK / HPK</t>
+          <t>AD↓ + M/T ≥25% + DP</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Hipoquinesia</t>
+          <t>Compromiso hemodinámico</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Disminución del movimiento del segmento indicado (segmentos y niveles en mayúscula o minúscula)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Según extensión</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Combina segmento (AS,A,L,I,P) + nivel (B,M,A)</t>
+          <t>"Derrame pericárdico con signos de aumento de presión intrapericárdica y compromiso hemodinámico" (+ "Inflamación" si PERIC presente)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2268,27 +2268,27 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>HPQ / HPQ GRAL / HPKG / HPKGRAL</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Hipoquinesia generalizada</t>
+          <t>Aquinesia</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Disminución difusa de la contractilidad del VI</t>
+          <t>Ausencia de movimiento del segmento indicado</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Severa</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>No implica obligatoriamente infarto antiguo</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>DSK</t>
+          <t>HK / HPK</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Discinesia</t>
+          <t>Hipoquinesia</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Movimiento paradójico del segmento indicado</t>
+          <t>Disminución del movimiento del segmento indicado (segmentos y niveles en mayúscula o minúscula)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Severa</t>
+          <t>Según extensión</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Sugiere aneurisma/necrosis</t>
+          <t>Combina segmento (AS,A,L,I,P) + nivel (B,M,A)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2342,27 +2342,27 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>HPQ / HPQ GRAL / HPKG / HPKGRAL</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Contractilidad conservada</t>
+          <t>Hipoquinesia generalizada</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Contractilidad segmentaria globalmente conservada</t>
+          <t>Disminución difusa de la contractilidad del VI</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Exclusión mutua: si OK, no coexisten trastornos segmentarios</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2379,27 +2379,27 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Seg?</t>
+          <t>DSK</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>No valorable</t>
+          <t>Discinesia</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Contractilidad segmentaria no valorable adecuadamente</t>
+          <t>Movimiento paradójico del segmento indicado</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Severa</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sugiere aneurisma/necrosis</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2411,32 +2411,32 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Válvula mitral</t>
+          <t>Contractilidad</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>EM</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis mitral</t>
+          <t>Contractilidad conservada</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis valvular mitral</t>
+          <t>Contractilidad segmentaria globalmente conservada</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis valvular mitral" (+ insuficiencia si coexiste)</t>
+          <t>Exclusión mutua: si OK, no coexisten trastornos segmentarios</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2448,22 +2448,22 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Válvula mitral</t>
+          <t>Contractilidad</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>EMB</t>
+          <t>Seg?</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis mitral + engrosamiento borde</t>
+          <t>No valorable</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis valvular con engrosamiento del borde de sus velos</t>
+          <t>Contractilidad segmentaria no valorable adecuadamente</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis y engrosamiento valvular mitral" (+ insuficiencia)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>EM</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis y calcificación valvular mitral</t>
+          <t>Esclerosis mitral</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis y calcificación valvular mitral (general, sin patrón específico)</t>
+          <t>Esclerosis valvular mitral</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis y calcificación valvular mitral" (+ insuficiencia si coexiste)</t>
+          <t>Conclusión: "Esclerosis valvular mitral" (+ insuficiencia si coexiste)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2527,17 +2527,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CM..</t>
+          <t>EMB</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis mitral + puntos de calcio</t>
+          <t>Esclerosis mitral + engrosamiento borde</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis valvular con puntos de calcio en sus velos</t>
+          <t>Esclerosis valvular con engrosamiento del borde de sus velos</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis valvular mitral con calcificación puntiforme" (+ insuficiencia)</t>
+          <t>Conclusión: "Esclerosis y engrosamiento valvular mitral" (+ insuficiencia)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>CMB</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Calcificación del borde de los velos</t>
+          <t>Esclerosis y calcificación valvular mitral</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis con calcificación del borde de sus velos</t>
+          <t>Esclerosis y calcificación valvular mitral (general, sin patrón específico)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis y calcificación del borde valvular mitral" (+ insuficiencia)</t>
+          <t>Conclusión: "Esclerosis y calcificación valvular mitral" (+ insuficiencia si coexiste)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>CM↑</t>
+          <t>CM..</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Engrosamiento/esclerosis/calcificación difusa</t>
+          <t>Esclerosis mitral + puntos de calcio</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Engrosamiento, esclerosis y calcificación valvular mitral</t>
+          <t>Esclerosis valvular con puntos de calcio en sus velos</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis, engrosamiento y calcificación valvular mitral" (+ insuficiencia). ↑ = engrosamiento</t>
+          <t>Conclusión: "Esclerosis valvular mitral con calcificación puntiforme" (+ insuficiencia)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2638,17 +2638,17 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>CMB</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Calcio velo posterior</t>
+          <t>Calcificación del borde de los velos</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Calcio en el velo posterior de la válvula mitral</t>
+          <t>Esclerosis con calcificación del borde de sus velos</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Calcificación del velo posterior mitral." No infiere estenosis sin SM/AVM</t>
+          <t>Conclusión: "Esclerosis y calcificación del borde valvular mitral" (+ insuficiencia)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>CMP↓</t>
+          <t>CM↑</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Calcio velo posterior + restricción</t>
+          <t>Engrosamiento/esclerosis/calcificación difusa</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Calcio en velo posterior con restricción de su excursión</t>
+          <t>Engrosamiento, esclerosis y calcificación valvular mitral</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "...con restricción de su movilidad." No infiere estenosis sin SM/AVM</t>
+          <t>Conclusión: "Esclerosis, engrosamiento y calcificación valvular mitral" (+ insuficiencia). ↑ = engrosamiento</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -2712,27 +2712,27 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>IM (T/leve/2/M/3/4)</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Insuficiencia valvular mitral</t>
+          <t>Calcio velo posterior</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Jet de regurgitación (leve→severa), central hacia AI salvo excéntrica</t>
+          <t>Calcio en el velo posterior de la válvula mitral</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Sin número=leve; 2=leve-mod; M=moderada; 3=mod-severa; 4=severa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Triviales SIEMPRE en conclusiones. "Insuficiencia valvular mitral [grado]". Se integra con AI/DD si coexisten</t>
+          <t>Conclusión: "Calcificación del velo posterior mitral." No infiere estenosis sin SM/AVM</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2749,17 +2749,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>IM# lat / inf / medial (m)</t>
+          <t>CMP↓</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>IM excéntrica</t>
+          <t>Calcio velo posterior + restricción</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Jet excéntrico dirigido hacia pared lateral/inferior/medial de la AI</t>
+          <t>Calcio en velo posterior con restricción de su excursión</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Conclusión solo agrega "excéntrica" (sin repetir dirección)</t>
+          <t>Conclusión: "...con restricción de su movilidad." No infiere estenosis sin SM/AVM</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>PM1</t>
+          <t>IM (T/leve/2/M/3/4)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Prolapso mitral (grado anatómico 1)</t>
+          <t>Insuficiencia valvular mitral</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Velos normales, adecuada apertura/cierre, que se aproxima al plano del anillo</t>
+          <t>Jet de regurgitación (leve→severa), central hacia AI salvo excéntrica</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sin número=leve; 2=leve-mod; M=moderada; 3=mod-severa; 4=severa</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Conclusión unificada: "Prolapso valvular mitral" (sin gradación). PROL retirado</t>
+          <t>Triviales SIEMPRE en conclusiones. "Insuficiencia valvular mitral [grado]". Se integra con AI/DD si coexisten</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>PM2</t>
+          <t>IM# lat / inf / medial (m)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Prolapso mitral (grado anatómico 2)</t>
+          <t>IM excéntrica</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>...que rectifica y alcanza el plano valvular del anillo</t>
+          <t>Jet excéntrico dirigido hacia pared lateral/inferior/medial de la AI</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Conclusión unificada: "Prolapso valvular mitral"</t>
+          <t>Conclusión solo agrega "excéntrica" (sin repetir dirección)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2860,17 +2860,17 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>PM3</t>
+          <t>PM1</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Prolapso mitral (grado anatómico 3)</t>
+          <t>Prolapso mitral (grado anatómico 1)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>...que sobrepasa el plano valvular del anillo hacia la AI</t>
+          <t>Velos normales, adecuada apertura/cierre, que se aproxima al plano del anillo</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Conclusión unificada: "Prolapso valvular mitral"</t>
+          <t>Conclusión unificada: "Prolapso valvular mitral" (sin gradación). PROL retirado</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -2897,27 +2897,27 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>PM2</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Estenosis mitral (limitación de apertura)</t>
+          <t>Prolapso mitral (grado anatómico 2)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>"Válvula mitral con limitación para su apertura."</t>
+          <t>...que rectifica y alcanza el plano valvular del anillo</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sin AVM: no concluye severidad</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Severidad se basa en AVM, no en SM</t>
+          <t>Conclusión unificada: "Prolapso valvular mitral"</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>DOMO</t>
+          <t>PM3</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Apertura en domo</t>
+          <t>Prolapso mitral (grado anatómico 3)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>"...con apertura en domo del velo anterior."</t>
+          <t>...que sobrepasa el plano valvular del anillo hacia la AI</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Se integra con SM/AVM</t>
+          <t>Conclusión unificada: "Prolapso valvular mitral"</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -2971,32 +2971,32 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>AVM</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Área valvular mitral (hemipresión)</t>
+          <t>Estenosis mitral (limitación de apertura)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Área valvular de xx cm²</t>
+          <t>"Válvula mitral con limitación para su apertura."</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Normal 4-6; leve &gt;1.5; moderada 1.0-1.5; severa &lt;1.0</t>
+          <t>Sin AVM: no concluye severidad</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Determina severidad de estenosis mitral</t>
+          <t>Severidad se basa en AVM, no en SM</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>ASE / ACC-AHA / ESC</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -3008,27 +3008,27 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>PVMM</t>
+          <t>DOMO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Prótesis Valvular Mitral Mecánica</t>
+          <t>Apertura en domo</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Prótesis mecánica en posición mitral</t>
+          <t>"...con apertura en domo del velo anterior."</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Normofuncionante/disfuncionante</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Nomenclatura estandarizada: P(prótesis)+V(valvular)+A/M(aórtica/mitral)+M/B(mecánica/biológica). Reemplaza PVBM/PMM antiguos</t>
+          <t>Se integra con SM/AVM</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3045,64 +3045,64 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>PVMB</t>
+          <t>AVM</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Prótesis Valvular Mitral Biológica</t>
+          <t>Área valvular mitral (hemipresión)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Prótesis biológica en posición mitral</t>
+          <t>Área valvular de xx cm²</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Normofuncionante/disfuncionante</t>
+          <t>Normal 4-6; leve &gt;1.5; moderada 1.0-1.5; severa &lt;1.0</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>"Prótesis valvular mitral normofuncionante" si mecanismo oclusor funcionante</t>
+          <t>Determina severidad de estenosis mitral</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE / ACC-AHA / ESC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Válvula aórtica</t>
+          <t>Válvula mitral</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>PVMM</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis aórtica</t>
+          <t>Prótesis Valvular Mitral Mecánica</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis valvular aórtica</t>
+          <t>Prótesis mecánica en posición mitral</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Normofuncionante/disfuncionante</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis valvular aórtica" (+ insuficiencia si coexiste)</t>
+          <t>Nomenclatura estandarizada: P(prótesis)+V(valvular)+A/M(aórtica/mitral)+M/B(mecánica/biológica). Reemplaza PVBM/PMM antiguos</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3114,32 +3114,32 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Válvula aórtica</t>
+          <t>Válvula mitral</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>EAB</t>
+          <t>PVMB</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis + engrosamiento borde</t>
+          <t>Prótesis Valvular Mitral Biológica</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis con engrosamiento del borde de sus hojuelas</t>
+          <t>Prótesis biológica en posición mitral</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Normofuncionante/disfuncionante</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis y leve engrosamiento valvular aórtico" (+ insuficiencia)</t>
+          <t>"Prótesis valvular mitral normofuncionante" si mecanismo oclusor funcionante</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>EA..</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis + puntos de calcio</t>
+          <t>Esclerosis aórtica</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis con puntos de calcio</t>
+          <t>Esclerosis valvular aórtica</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis valvular aórtica con calcificación puntiforme" (+ insuficiencia)</t>
+          <t>Conclusión: "Esclerosis valvular aórtica" (+ insuficiencia si coexiste)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3193,17 +3193,17 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>CAB</t>
+          <t>EAB</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Calcificación del borde de hojuelas</t>
+          <t>Esclerosis + engrosamiento borde</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis con calcificación del borde de sus hojuelas</t>
+          <t>Esclerosis con engrosamiento del borde de sus hojuelas</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis y calcificación del borde valvular aórtico" (+ insuficiencia)</t>
+          <t>Conclusión: "Esclerosis y leve engrosamiento valvular aórtico" (+ insuficiencia)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3230,17 +3230,17 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>CA↑</t>
+          <t>EA..</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Engrosamiento/esclerosis/calcificación difusa</t>
+          <t>Esclerosis + puntos de calcio</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Engrosamiento, esclerosis y calcificación valvular aórtica</t>
+          <t>Esclerosis con puntos de calcio</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Esclerosis, engrosamiento y calcificación valvular aórtica" (+ insuficiencia)</t>
+          <t>Conclusión: "Esclerosis valvular aórtica con calcificación puntiforme" (+ insuficiencia)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Válvula mitral / aórtica</t>
+          <t>Válvula aórtica</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>ANILLO</t>
+          <t>CAB</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Calcio en el anillo valvular</t>
+          <t>Calcificación del borde de hojuelas</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Calcio en anillo valvular correspondiente (mitral o aórtico)</t>
+          <t>Esclerosis con calcificación del borde de sus hojuelas</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Leve/moderado/severo si se especifica</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "...con [leve] calcio en su anillo." Se integra con la morfología de esa válvula (recuperado del diccionario original, faltaba en consolidación previa)</t>
+          <t>Conclusión: "Esclerosis y calcificación del borde valvular aórtico" (+ insuficiencia)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3304,27 +3304,27 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>IA (1-4)</t>
+          <t>CA↑</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Insuficiencia valvular aórtica</t>
+          <t>Engrosamiento/esclerosis/calcificación difusa</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Jet de regurgitación (leve→severa), central hacia TSVI salvo excéntrica</t>
+          <t>Engrosamiento, esclerosis y calcificación valvular aórtica</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Misma escala que IM (leve/leve-mod/mod/mod-severa/severa)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>"Insuficiencia valvular aórtica [grado]"</t>
+          <t>Conclusión: "Esclerosis, engrosamiento y calcificación valvular aórtica" (+ insuficiencia)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3336,32 +3336,32 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Válvula aórtica</t>
+          <t>Válvula mitral / aórtica</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>IA exc sep</t>
+          <t>ANILLO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>IA excéntrica hacia septum</t>
+          <t>Calcio en el anillo valvular</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Jet excéntrico dirigido al septum interventricular</t>
+          <t>Calcio en anillo valvular correspondiente (mitral o aórtico)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Leve/moderado/severo si se especifica</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Conclusión solo agrega "excéntrica"</t>
+          <t>Conclusión: "...con [leve] calcio en su anillo." Se integra con la morfología de esa válvula (recuperado del diccionario original, faltaba en consolidación previa)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3378,27 +3378,27 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>IA exc EM / ex mit</t>
+          <t>IA (1-4)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>IA excéntrica hacia mitral</t>
+          <t>Insuficiencia valvular aórtica</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Jet excéntrico dirigido al velo anterior mitral (sinónimos)</t>
+          <t>Jet de regurgitación (leve→severa), central hacia TSVI salvo excéntrica</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Misma escala que IM (leve/leve-mod/mod/mod-severa/severa)</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Conclusión solo agrega "excéntrica"</t>
+          <t>"Insuficiencia valvular aórtica [grado]"</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3415,17 +3415,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>COANDA</t>
+          <t>IA exc sep</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Efecto Coanda</t>
+          <t>IA excéntrica hacia septum</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Jet excéntrico con efecto Coanda</t>
+          <t>Jet excéntrico dirigido al septum interventricular</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Conclusión solo agrega "excéntrica"</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3452,27 +3452,27 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IA exc EM / ex mit</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Estenosis aórtica (limitación de apertura)</t>
+          <t>IA excéntrica hacia mitral</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>"Válvula aórtica con limitación para su apertura."</t>
+          <t>Jet excéntrico dirigido al velo anterior mitral (sinónimos)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Ver criterios de gradiente/AVA</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Conclusión solo agrega "excéntrica"</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3489,27 +3489,27 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>A ##/</t>
+          <t>COANDA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Gradiente pico solo (sin medio)</t>
+          <t>Efecto Coanda</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>"Gradiente pico de xx mmHg."</t>
+          <t>Jet excéntrico con efecto Coanda</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Leve &lt;34; moderada 34-64; severa ≥64 mmHg (equivalente Bernoulli 4V²)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Se usa solo si no hay gradiente medio disponible</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3526,32 +3526,32 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>A ##/##</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Gradiente pico / medio</t>
+          <t>Estenosis aórtica (limitación de apertura)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>"Gradiente pico de xx mmHg y gradiente medio de xx mmHg."</t>
+          <t>"Válvula aórtica con limitación para su apertura."</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Medio: leve &lt;20; moderada 20-39; severa ≥40 mmHg</t>
+          <t>Ver criterios de gradiente/AVA</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Gradiente medio tiene prioridad sobre el pico si ambos están disponibles</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>ASE / ACC-AHA / ESC</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -3563,32 +3563,32 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>AVA</t>
+          <t>A ##/</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Área valvular aórtica</t>
+          <t>Gradiente pico solo (sin medio)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Área valvular de xx cm² por continuidad</t>
+          <t>"Gradiente pico de xx mmHg."</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Leve &gt;1.5; moderada 1.0-1.5; severa &lt;1.0</t>
+          <t>Leve &lt;34; moderada 34-64; severa ≥64 mmHg (equivalente Bernoulli 4V²)</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Confirma/complementa gradiente</t>
+          <t>Se usa solo si no hay gradiente medio disponible</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>ASE / ACC-AHA / ESC</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -3600,32 +3600,32 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>PVAM</t>
+          <t>A ##/##</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Prótesis Valvular Aórtica Mecánica</t>
+          <t>Gradiente pico / medio</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Prótesis mecánica en posición aórtica</t>
+          <t>"Gradiente pico de xx mmHg y gradiente medio de xx mmHg."</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Normofuncionante/disfuncionante</t>
+          <t>Medio: leve &lt;20; moderada 20-39; severa ≥40 mmHg</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Misma nomenclatura estandarizada. Reemplaza PMA antiguo</t>
+          <t>Gradiente medio tiene prioridad sobre el pico si ambos están disponibles</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE / ACC-AHA / ESC</t>
         </is>
       </c>
     </row>
@@ -3637,64 +3637,64 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>PVAB</t>
+          <t>AVA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Prótesis Valvular Aórtica Biológica</t>
+          <t>Área valvular aórtica</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Prótesis biológica en posición aórtica</t>
+          <t>Área valvular de xx cm² por continuidad</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Normofuncionante/disfuncionante</t>
+          <t>Leve &gt;1.5; moderada 1.0-1.5; severa &lt;1.0</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>"Prótesis valvular aórtica normofuncionante" si mecanismo oclusor funcionante. Reemplaza PVBA antiguo</t>
+          <t>Confirma/complementa gradiente</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE / ACC-AHA / ESC</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Válvula tricúspide</t>
+          <t>Válvula aórtica</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>PVAM</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis tricuspídea</t>
+          <t>Prótesis Valvular Aórtica Mecánica</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis valvular tricuspídea</t>
+          <t>Prótesis mecánica en posición aórtica</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Normofuncionante/disfuncionante</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Misma nomenclatura estandarizada. Reemplaza PMA antiguo</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3706,32 +3706,32 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Válvula tricúspide</t>
+          <t>Válvula aórtica</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>IT (1-4)</t>
+          <t>PVAB</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Insuficiencia valvular tricuspídea</t>
+          <t>Prótesis Valvular Aórtica Biológica</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Jet de regurgitación graduado</t>
+          <t>Prótesis biológica en posición aórtica</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Misma escala que IM</t>
+          <t>Normofuncionante/disfuncionante</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>"Insuficiencia valvular tricuspídea [grado]"; se integra con Sxx y PSAP en HP</t>
+          <t>"Prótesis valvular aórtica normofuncionante" si mecanismo oclusor funcionante. Reemplaza PVBA antiguo</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3748,17 +3748,17 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>S-xx / S:xx</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Gradiente pico sistólico de IT</t>
+          <t>Esclerosis tricuspídea</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Jet tricuspídeo con gradiente pico sistólico de xx mmHg. Convención oficial: separar con guion o dos puntos (S-45/S:45) para evitar confusión con un número puro (ej. "545").</t>
+          <t>Esclerosis valvular tricuspídea</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Siempre gradiente PICO sistólico</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3785,27 +3785,27 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>VC ##</t>
+          <t>IT (1-4)</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Vena contracta</t>
+          <t>Insuficiencia valvular tricuspídea</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Vena contracta estimada en xx cm, sigue a la lesión</t>
+          <t>Jet de regurgitación graduado</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Misma escala que IM</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>No concluye sola</t>
+          <t>"Insuficiencia valvular tricuspídea [grado]"; se integra con Sxx y PSAP en HP</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3822,27 +3822,27 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>S-xx / S:xx</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Estenosis tricuspídea</t>
+          <t>Gradiente pico sistólico de IT</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Estenosis tricuspídea</t>
+          <t>Jet tricuspídeo con gradiente pico sistólico de xx mmHg. Convención oficial: separar con guion o dos puntos (S-45/S:45) para evitar confusión con un número puro (ej. "545").</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Según severidad</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Siempre gradiente PICO sistólico</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3854,22 +3854,22 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Válvula pulmonar</t>
+          <t>Válvula tricúspide</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>VC ##</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Insuficiencia valvular pulmonar</t>
+          <t>Vena contracta</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Jet de regurgitación con gradiente diastólico de xx mmHg</t>
+          <t>Vena contracta estimada en xx cm, sigue a la lesión</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Se usa "insuficiencia VALVULAR pulmonar" para no confundir con patología del pulmón</t>
+          <t>No concluye sola</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3891,32 +3891,32 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Válvula pulmonar</t>
+          <t>Válvula tricúspide</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>EP</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis valvular pulmonar</t>
+          <t>Estenosis tricuspídea</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Esclerosis valvular pulmonar</t>
+          <t>Estenosis tricuspídea</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Según severidad</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Corrige definición previa (antes combinada por error con SP)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3933,27 +3933,27 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Estenosis valvular pulmonar</t>
+          <t>Insuficiencia valvular pulmonar</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Estenosis valvular pulmonar</t>
+          <t>Jet de regurgitación con gradiente diastólico de xx mmHg</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Según gradiente</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Se usa "insuficiencia VALVULAR pulmonar" para no confundir con patología del pulmón</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3965,22 +3965,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Diástole / Doppler</t>
+          <t>Válvula pulmonar</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>E/A ##/##</t>
+          <t>EP</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Ondas E y A</t>
+          <t>Esclerosis valvular pulmonar</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Onda E de xx cm/seg y onda A de xx cm/seg</t>
+          <t>Esclerosis valvular pulmonar</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3990,39 +3990,39 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Base de clasificación diastólica</t>
+          <t>Corrige definición previa (antes combinada por error con SP)</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>ASE 2025</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Diástole / Doppler</t>
+          <t>Válvula pulmonar</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>E' ##</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Onda E' tisular</t>
+          <t>Estenosis valvular pulmonar</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Onda E' tisular de xx cm/seg</t>
+          <t>Estenosis valvular pulmonar</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Según gradiente</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>ASE 2025</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -4044,27 +4044,27 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>E/e ##</t>
+          <t>E/A ##/##</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Relación E/e'</t>
+          <t>Ondas E y A</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Relación E/e' (presión de llenado)</t>
+          <t>Onda E de xx cm/seg y onda A de xx cm/seg</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Según valor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Parámetro clave (enfoque ASE 2025)</t>
+          <t>Base de clasificación diastólica</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -4081,17 +4081,17 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>DT ## / TD ##</t>
+          <t>E' ##</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Tiempo de desaceleración (sinónimos)</t>
+          <t>Onda E' tisular</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Tiempo de desaceleración de xx ms</t>
+          <t>Onda E' tisular de xx cm/seg</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>DT y TD son intercambiables, mismo significado</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>ASE 2015</t>
+          <t>ASE 2025</t>
         </is>
       </c>
     </row>
@@ -4118,32 +4118,32 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>TRI ##</t>
+          <t>E/e ##</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Tiempo de relajación isovolumétrica</t>
+          <t>Relación E/e'</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>"Inversión de la relación de ondas E:A, con tiempo de relajación isovolumétrica de xx ms."</t>
+          <t>Relación E/e' (presión de llenado)</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Descriptivo (fuera del algoritmo de grado)</t>
+          <t>Según valor</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Ya NO participa en el cálculo del grado de disfunción diastólica (algoritmo Nagueh 2016); queda como hallazgo puramente descriptivo</t>
+          <t>Parámetro clave (enfoque ASE 2025)</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE 2025</t>
         </is>
       </c>
     </row>
@@ -4155,32 +4155,32 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>E' (sin sufijo)</t>
+          <t>DT ## / TD ##</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Onda E' tisular LATERAL (default)</t>
+          <t>Tiempo de desaceleración (sinónimos)</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Onda E' lateral de xx cm/seg</t>
+          <t>Tiempo de desaceleración de xx ms</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>&lt;10 cm/s = criterio positivo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Usado en algoritmo de disfunción diastólica</t>
+          <t>DT y TD son intercambiables, mismo significado</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>ASE 2016 (Nagueh)</t>
+          <t>ASE 2015</t>
         </is>
       </c>
     </row>
@@ -4192,32 +4192,32 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>E' sep / E' septal</t>
+          <t>TRI ##</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Onda E' tisular SEPTAL</t>
+          <t>Tiempo de relajación isovolumétrica</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Onda E' septal de xx cm/seg</t>
+          <t>"Inversión de la relación de ondas E:A, con tiempo de relajación isovolumétrica de xx ms."</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>&lt;7 cm/s = criterio positivo</t>
+          <t>Descriptivo (fuera del algoritmo de grado)</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Usado en algoritmo de disfunción diastólica</t>
+          <t>Ya NO participa en el cálculo del grado de disfunción diastólica (algoritmo Nagueh 2016); queda como hallazgo puramente descriptivo</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>ASE 2016 (Nagueh)</t>
+          <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
@@ -4229,32 +4229,32 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>DD1 / DD2 / DD3 (dictado directo)</t>
+          <t>E' (sin sufijo)</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Grado de disfunción diastólica (override manual)</t>
+          <t>Onda E' tisular LATERAL (default)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Se usa tal cual, sin recalcular</t>
+          <t>Onda E' lateral de xx cm/seg</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Grado 1/2/3</t>
+          <t>&lt;10 cm/s = criterio positivo</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Prioridad ABSOLUTA sobre el cálculo automático del algoritmo</t>
+          <t>Usado en algoritmo de disfunción diastólica</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE 2016 (Nagueh)</t>
         </is>
       </c>
     </row>
@@ -4266,64 +4266,64 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>TAPSE</t>
+          <t>E' sep / E' septal</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Excursión sistólica anular tricuspídea</t>
+          <t>Onda E' tisular SEPTAL</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>TAPSE en mm</t>
+          <t>Onda E' septal de xx cm/seg</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Según valor</t>
+          <t>&lt;7 cm/s = criterio positivo</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Función VD; se integra en HP</t>
+          <t>Usado en algoritmo de disfunción diastólica</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>ASE 2025</t>
+          <t>ASE 2016 (Nagueh)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Hipertensión pulmonar</t>
+          <t>Diástole / Doppler</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Sxx (aislado, sin otros datos)</t>
+          <t>DD1 / DD2 / DD3 (dictado directo)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Probabilidad de HP basada solo en gradiente de IT</t>
+          <t>Grado de disfunción diastólica (override manual)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Se usa tal cual, sin recalcular</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>≤40 mmHg = baja; &gt;40 mmHg = intermedia</t>
+          <t>Grado 1/2/3</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Sxx SÍ concluye probabilidad por sí solo (corrige regla previa). La probabilidad de HP es independiente de la severidad de la IT; la conclusión NUNCA repite el grado de la IT, solo el nivel de probabilidad</t>
+          <t>Prioridad ABSOLUTA sobre el cálculo automático del algoritmo</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -4335,69 +4335,69 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Hipertensión pulmonar</t>
+          <t>Diástole / Doppler</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Sxx &gt;40 + D↑/AD↑/S-S-S-D-S-SD/CAV↓/TAPSE bajo</t>
+          <t>TAPSE</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Probabilidad de HP con hallazgos de sobrecarga derecha adicionales</t>
+          <t>Excursión sistólica anular tricuspídea</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Integración automática de sobrecarga derecha</t>
+          <t>TAPSE en mm</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Alta probabilidad</t>
+          <t>Según valor</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Conclusión: "Alta probabilidad para hipertensión pulmonar con [hallazgos asociados]"</t>
+          <t>Función VD; se integra en HP</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>ASE 2025 / ESC</t>
+          <t>ASE 2025</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Masas y dispositivos</t>
+          <t>Hipertensión pulmonar</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>TX / TXM / TXMU / TXP / TXO</t>
+          <t>Sxx (aislado, sin otros datos)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Trombo (general/móvil/mural/pediculado/organizado)</t>
+          <t>Probabilidad de HP basada solo en gradiente de IT</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Imagen compatible con trombo de xx × xx mm en [localización]</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≤40 mmHg = baja; &gt;40 mmHg = intermedia</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Máxima prioridad en conclusiones. TX en VI → asociar infarto/miocardiopatía; TX en AI/OI → asociar FA</t>
+          <t>Sxx SÍ concluye probabilidad por sí solo (corrige regla previa). La probabilidad de HP es independiente de la severidad de la IT; la conclusión NUNCA repite el grado de la IT, solo el nivel de probabilidad</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -4409,37 +4409,37 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Masas y dispositivos</t>
+          <t>Hipertensión pulmonar</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>CE / HUMO / SMOK / SMOCK</t>
+          <t>Sxx &gt;40 + D↑/AD↑/S-S-S-D-S-SD/CAV↓/TAPSE bajo</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Contraste espontáneo</t>
+          <t>Probabilidad de HP con hallazgos de sobrecarga derecha adicionales</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Contraste espontáneo intracavitario</t>
+          <t>Integración automática de sobrecarga derecha</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Sin especificar</t>
+          <t>Alta probabilidad</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Sinónimos; CE+AI dilatada / CE+FA / CE+FEVI↓ → asociaciones clínicas de riesgo</t>
+          <t>Conclusión: "Alta probabilidad para hipertensión pulmonar con [hallazgos asociados]"</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>ORTIZNOR</t>
+          <t>ASE 2025 / ESC</t>
         </is>
       </c>
     </row>
@@ -4451,27 +4451,27 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>CE1 / CE2 / CE3</t>
+          <t>TX / TXM / TXMU / TXP / TXO</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Grados de contraste espontáneo</t>
+          <t>Trombo (general/móvil/mural/pediculado/organizado)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Leve/moderado/severo</t>
+          <t>Imagen compatible con trombo de xx × xx mm en [localización]</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Leve/moderado/severo</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Máxima prioridad en conclusiones. TX en VI → asociar infarto/miocardiopatía; TX en AI/OI → asociar FA</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4488,27 +4488,27 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>VEG / MIX / TUM / FIB / LIP / CALC / CAT / ELEC / DIS / CHI / EUS</t>
+          <t>CE / HUMO / SMOK / SMOCK</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Otras masas y dispositivos</t>
+          <t>Contraste espontáneo</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Ver descripción específica por código</t>
+          <t>Contraste espontáneo intracavitario</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Sin especificar</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>VEG→endocarditis; MIX→tumor 1°; FIB→fibroelastoma (asociaciones orientadoras, no reemplazan juicio clínico)</t>
+          <t>Sinónimos; CE+AI dilatada / CE+FA / CE+FEVI↓ → asociaciones clínicas de riesgo</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -4520,32 +4520,32 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Ritmo / condiciones</t>
+          <t>Masas y dispositivos</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>FA</t>
+          <t>CE1 / CE2 / CE3</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Fibrilación auricular</t>
+          <t>Grados de contraste espontáneo</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Ritmo de FA con respuesta ventricular promedio de xx/min</t>
+          <t>Leve/moderado/severo</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Leve/moderado/severo</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>Reemplaza "ritmo sinusal" en la frase de apertura</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -4557,22 +4557,22 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Ritmo / condiciones</t>
+          <t>Masas y dispositivos</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Flutter / FLUT / Fluter</t>
+          <t>VEG / MIX / TUM / FIB / LIP / CALC / CAT / DIS / CHI / EUS</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Flutter auricular (sinónimos)</t>
+          <t>Otras masas y dispositivos</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Flutter auricular con respuesta ventricular promedio de xx/min</t>
+          <t>Ver descripción específica por código</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Reemplaza ritmo en frase de apertura</t>
+          <t>VEG→endocarditis; MIX→tumor 1°; FIB→fibroelastoma (asociaciones orientadoras, no reemplazan juicio clínico). ELEC tiene entrada propia (ver abajo)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -4594,22 +4594,22 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Ritmo / condiciones</t>
+          <t>Masas y dispositivos</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>MCPS / MP</t>
+          <t>ELEC / ELECT</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Marcapasos (sinónimos)</t>
+          <t>Electrodo de estimulación (ELECT es sinónimo, autocorrector iPhone)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Ritmo de estimulación por marcapasos</t>
+          <t>Presencia de electrodo de estimulación en cavidades derechas</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Reemplaza ritmo en frase de apertura</t>
+          <t>SIEMPRE genérico ("cavidades derechas"), sin importar si se especifica localización o medidas junto al código</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>IOT</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Intubación</t>
+          <t>Fibrilación auricular</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Paciente intubado en ventilación mecánica</t>
+          <t>Ritmo de FA con respuesta ventricular promedio de xx/min</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Se agrega a frase de apertura si fue dictado</t>
+          <t>Reemplaza "ritmo sinusal" en la frase de apertura</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4673,17 +4673,17 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>INMOVIL / DECUBITO</t>
+          <t>Flutter / FLUT / Fluter</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Condición del estudio</t>
+          <t>Flutter auricular (sinónimos)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Estudio realizado en paciente inmovilizado en decúbito dorsal</t>
+          <t>Flutter auricular con respuesta ventricular promedio de xx/min</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -4693,17 +4693,313 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
+          <t>Reemplaza ritmo en frase de apertura</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>MCPS / MP</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Marcapasos (sinónimos)</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo de estimulación por marcapasos</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Reemplaza ritmo en frase de apertura</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>IOT</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Intubación</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Paciente intubado en ventilación mecánica</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
           <t>Se agrega a frase de apertura si fue dictado</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>INMOV / INMOVIL / INMOVILIZADO</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Paciente inmovilizado (implica también decúbito dorsal)</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Paciente inmovilizado en decúbito dorsal</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Se agrega a frase de apertura si fue dictado. Distinto de DECUBITO/DORSAL solo (que no implica inmovilización)</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>DECUBITO / DORSAL</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Posición del paciente (sin implicar inmovilización)</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Paciente en decúbito dorsal</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Distinto de INMOV/INMOVILIZADO (que sí implica inmovilización además de la posición)</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>SS / SEMISENT / SEMISENTADO</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Posición semisentada</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Paciente semisentado</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Se agrega a frase de apertura si fue dictado</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>SILLA</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Paciente sentado en silla</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Paciente sentado en silla</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Se agrega a frase de apertura si fue dictado</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>GRANULADO</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Patrón infiltrativo miocárdico</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Se aprecia patrón de puntuado en espesor del miocardio ventricular izquierdo que sugiere infiltración</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Conclusión: "Patrón de puntuado en el espesor del miocardio ventricular izquierdo que sugiere infiltración." No recomienda estudio adicional (regla general)</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>(automático) Septum y PP</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Detección automática de hipertrofia</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Si NO se codificó HVI manualmente, y septum Y pared posterior (ambas) son &gt;1.1 cm, el sistema agrega automáticamente "Hipertrofia de sus paredes"</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Corte: &gt;1.1 cm en AMBAS paredes (no basta con una sola)</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Conclusión automática: "HIPERTROFIA VENTRICULAR IZQUIERDA."</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>ORTIZNOR</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G114"/>
+  <autoFilter ref="A1:G120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4714,7 +5010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -4985,8 +5281,116 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Tolerancia cama + nombre en una línea</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Si el médico escribe cama y nombre juntos en la primera línea (ej. "317 Sergio Hernández"), el sistema los separa automáticamente (primer token = cama, resto = nombre), sin necesidad de que estén en líneas separadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Jets de regurgitación van en Doppler, no en Válvulas</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>La descripción de Válvulas contiene solo morfología (esclerosis/calcificación/estenosis); todos los jets de regurgitación (mitral, aórtica, pulmonar, tricuspídea) se describen en la sección Doppler, con su severidad y dirección (central/excéntrico).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Morfología mitral nunca deja base "normal" contradictoria</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Si hay CMP, CM, EM (o cualquier hallazgo morfológico mitral) sin insuficiencia, la descripción no debe decir "Mitral normal"; usa base neutra "Mitral excursionando adecuadamente" y agrega el hallazgo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Contractilidad global sigue la FEVI real</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>"Contractilidad global conservada" solo si FEVI≥50%; si FEVI&lt;50%, dice "disminuida". Nunca fija en "conservada" por defecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Dirección excéntrica sin contradicción</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Si el jet es excéntrico, la descripción dice "excéntrico hacia [estructura]", nunca combina "excéntrico" y "central" en la misma frase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>HVI/hipertrofia siempre genera conclusión propia</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Tanto si se codifica manualmente (HVI/LHVI) como si se detecta automáticamente por medidas, debe generar la línea de conclusión "HIPERTROFIA VENTRICULAR IZQUIERDA" (o "LEVE...").</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Dilatación de cavidades derechas no se duplica con HP</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Si hay dato de gradiente de IT (Sxx), la dilatación de cavidades derechas (Apex bi/der) se integra dentro de la conclusión de probabilidad de hipertensión pulmonar, no aparece como línea aparte. Solo aparece sola si no hay ningún dato de gradiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AI dilatada + insuficiencia mitral se integran</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Si coexisten AI dilatada/severa e insuficiencia mitral, se funden en una sola conclusión ("...CON DILATACION [SEVERA DE] AURICULA IZQUIERDA ASOCIADA"), nunca como dos conclusiones separadas. Si no hay insuficiencia mitral, la dilatación de AI se reporta sola.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Electrodo intracavitario implica ritmo de estimulación</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Si se detecta electrodo (ELEC/ELECT) y no se dictó explícitamente otro ritmo (FA/Flutter/MCPS), el ritmo por defecto de la frase de apertura cambia de "SINUSAL" a "ESTIMULACION POR MARCAPASOS".</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B22"/>
+  <autoFilter ref="A1:B31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ORTIZNOR_Tabla_Maestra.xlsx
+++ b/ORTIZNOR_Tabla_Maestra.xlsx
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diccionario Maestro'!$A$1:$G$120</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reglas de Redacción'!$A$1:$B$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Reglas de Redacción'!$A$1:$B$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Reglas Clínicas'!$A$1:$C$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4998,6 +4998,2707 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales / Apertura</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>H / M</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Sexo del paciente</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>No genera texto propio; habilita la clasificación del índice de masa VI</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>H (hombre): normal ≤115 g/m². M (mujer): normal ≤95 g/m²</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Sin este dato, el índice de masa VI se calcula y muestra pero no se clasifica como normal/anormal</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>ASE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>(automático) Índice de masa VI</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Índice de masa ventricular izquierda (Devereux)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Se calcula siempre que haya septum, pared posterior y VI diástole; se muestra en g/m² si hay SC (peso+talla)</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Normal: H ≤115 g/m², M ≤95 g/m²</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Si supera el corte según sexo, dispara automáticamente "HIPERTROFIA VENTRICULAR IZQUIERDA" en conclusiones (igual que la regla de septum+PP ambos &gt;1.1 cm; cualquiera de las dos activa la conclusión)</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>ASE 2015 (Devereux)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>ESV</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Extrasistolia supraventricular frecuente</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>"Frecuente extrasistolia supraventricular" (en bloque de condición)</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>También genera conclusión propia: "FRECUENTE EXTRASISTOLIA SUPRAVENTRICULAR."</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Extrasistolia ventricular frecuente</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>"Frecuente extrasistolia ventricular" (en bloque de condición)</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>También genera conclusión propia: "FRECUENTE EXTRASISTOLIA VENTRICULAR."</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>EXTRASIST</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Extrasistolia frecuente (tipo no especificado)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>"Frecuente extrasistolia" (en bloque de condición)</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>También genera conclusión propia: "FRECUENTE EXTRASISTOLIA."</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>TERNE</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Alineación oblicua del corte paraesternal largo</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>"Alineación oblicua del corte paraesternal largo" (en bloque de condición, nota técnica de calidad del estudio)</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>SEP VIBR</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Movimiento vibrado del septum interventricular</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>"Septum interventricular con movimiento vibrado."</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>TAPSE / TPS</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Excursión sistólica del plano anular tricuspídeo (sinónimos)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Usado en criterios de disfunción de VD e hipertensión pulmonar (TAPSE bajo &lt;17mm)</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>ASE 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>DER?</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Flujos Doppler en cavidades derechas no valorables</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>"Flujos Doppler en cavidades derechas no valorables." (en sección Doppler)</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades derechas</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>VD ## (pared libre, actualizado)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Pared libre del VD — ahora sí se describe y concluye</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>"Pared libre del ventrículo derecho de ## cm." (antes se capturaba el dato pero nunca se usaba)</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Hipertrofia si &gt;0.5 cm</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Si &gt;0.5 cm, se suma como "hipertrofia del ventrículo derecho" dentro de la conclusión integrada de hipertensión pulmonar (mismo mecanismo que dilatación de cavidades derechas)</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Pericardio</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>GRASA</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Grasa pericárdica</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>"Hipoecodensidad sugestiva de grasa pericárdica." Si coexiste con DP/DPP, se combina en una sola frase: "...asociado a hipoecodensidad sugestiva de grasa pericárdica."</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>IA SEPTAL</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Alias de IA exc sep (dirección excéntrica hacia septum)</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Mismo comportamiento que "IA exc sep"</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Pericardio</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>PERICARDIO</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Sinónimo de PERIC</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Igual comportamiento que PERIC</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>EM..</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Sinónimo de CM..</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Esclerosis valvular mitral con puntos de calcio en sus velos</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Mismo comportamiento que CM.. en descripción y conclusión</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Contractilidad</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>APEX↓ / APEX ↓</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Aquinesia del casquete apical</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>"Aquinesia del casquete apical" (se integra en el listado de alteraciones segmentarias)</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Genera conclusión de cardiopatía isquémica igual que otras alteraciones segmentarias</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Contractilidad</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>HPK GENERALIZADA</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Sinónimo del grupo hipoquinesia generalizada</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Igual que HPQ/HPKG/HPKGRAL</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Pericardio</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>GRS</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Grasa epicárdica (distinto de GRASA)</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>"Halo de hipoecodensidad anterior y apical."</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Conclusión propia: "PRESENCIA DE GRASA EN EPICARDIO." (no se combina con derrame como GRASA)</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Hipertensión pulmonar</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Cor pulmonale</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>No genera línea de descripción propia</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Fuerza automáticamente probabilidad ALTA</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Reemplaza el prefijo habitual: "COR PULMONALE CON ALTA PROBABILIDAD PARA HIPERTENSION PULMONAR CON [hallazgos asociados]." — incluso sin gradiente de IT</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>D IZQ</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Decúbito lateral izquierdo (posición mayoritaria)</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>No genera descripción (posición por defecto/esperada, se omite deliberadamente)</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Código reconocido pero silencioso, a diferencia de DD/DORSAL que sí se describen</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>D DER</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Decúbito lateral derecho (posición excepcional)</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>"Paciente en decúbito lateral derecho." (sí se describe, por ser posición atípica)</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>TAP ##</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Tiempo de aceleración pulmonar</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>"Tiempo de aceleración pulmonar de ## ms." (solo en Doppler)</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>No genera conclusión propia</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Contractilidad</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>AK-[pared]-[nivel] / HK-... / DK-...</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Trastorno segmentario (formato simplificado nuevo)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Pared: 1-3 letras de A/S/L/I/P (fusiona en término único si es par clásico: AS→anteroseptal, AL→anterolateral, IL→inferolateral, PL→posterolateral, IP→posteroinferior; si no, nombres separados). Nivel: 1-3 letras de A/M/B (apical/medial/basal, combinables)</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Ej: AK-AL-BM → Aquinesia anterolateral basal y medial. Coexiste con el formato viejo (AK/HK/HPK/DSK + segmento + nivel)</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>PAPILAR / PAPILARES</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Hipertrofia de músculos papilares</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Solo descriptivo, no genera conclusión propia</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Usualmente asociado a HVI</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>CUERDA (corregido)</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Falsa cuerda tendinosa VI</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Por defecto: "que va de la pared lateroapical al septum". Solo descriptivo</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Corrige descripción anatómica previa incorrecta</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>H / M (sexo)</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Sexo del paciente</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Habilita clasificación de índice de masa VI y patrón geométrico</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>H≤115 / M≤95 g/m²</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>ASE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>(automático) RWT y patrón geométrico</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Grosor relativo de pared + clasificación geométrica</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>RWT=2×PP/VIdiast, mostrado siempre en descripción junto al índice de masa</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>RWT≥0.42 = pared relativamente gruesa</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>4 patrones: hipertrofia concéntrica (masa alta+RWT alto), excéntrica (masa alta+RWT bajo), remodelado concéntrico (masa normal+RWT alto), remodelado excéntrico (masa normal+RWT bajo+VI dilatado)</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>ASE 2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>Raíz aórtica &gt;4.0cm (automático)</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Dilatación de raíz aórtica</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Integrada en la misma conclusión que esclerosis/regurgitación aórtica (no aparte)</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>&gt;4.0 cm</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>AO SINUSAL ## / AO ST ##</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Diámetro sinusal (senos Valsalva) / unión sinotubular, cuando dilatados</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Solo se dictan cuando están aumentados</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Dilatación aneurismática de aorta ascendente</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Con o sin medida asociada</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>AT ##</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Diámetro del arco aórtico transverso</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Descriptivo, sin clasificación automática</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Esclerosis y calcificación aórtica (paralelo a CM mitral)</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica/mitral</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>ANILLO (corregido)</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Calcio en anillo valvular</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Bug corregido: se capturaba pero nunca se describía/concluía (mitral) y el enrutamiento aórtica/mitral fallaba si había un código de la otra válvula antes</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Ahora se integra en la conclusión de la válvula correspondiente</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica/mitral</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>Dirección excéntrica (detallada)</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>IA exc sep/mit, IM lat/inf/medial ahora describen dirección específica</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>"hacia el septum interventricular", "hacia el velo anterior de la válvula mitral", "hacia la pared lateral/inferior/medial de la aurícula izquierda"</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Antes decía genéricamente "hacia TSVI"/"hacia aurícula izquierda" sin importar la dirección real</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>DD / DPL</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>DD=decúbito dorsal (sinónimo). DPL=derrame pleural izquierdo</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>DD→condición. DPL→Pericardio: "Zona de ausencia de ecos retrocardíacos", incidental</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>DPL en conclusión: "SUGIERE PRESENCIA DE DERRAME PLEURAL IZQUIERDO"</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>MCP / MP / MARCAP / MARCAPASO / MCPS</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Sinónimos de estimulación por dispositivo</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo: "ESTIMULACION DE DISPOSITIVO DE RITMO" (genérico, no asume marcapasos vs CDI vs resincronizador)</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>GD ## / GRAD DIN ##</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Gradiente dinámico intraventricular</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>"Presencia de gradiente dinámico intraventricular de ## mmHg."</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>IP## (con gradiente)</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Insuficiencia pulmonar con gradiente de fin de diástole</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>"Jet de regurgitación valvular pulmonar leve hacia infundíbulo con gradiente al final de diástole de ## mmHg."</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Función ventricular</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>Función ventricular fusionada con origen isquémico</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Cuando hay alteración segmentaria</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>"FUNCION VENTRICULAR IZQUIERDA [ESTADO] DE ORIGEN ISQUEMICO CON ALTERACIONES SEGMENTARIAS" (una sola conclusión, reemplaza a la antigua "CARDIOPATIA ISQUEMICA... NECROSIS O INFARTO")</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Ya no presume cronología (agudo/antiguo)</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Función ventricular</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>FE &lt;30% (automático)</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Función ventricular severamente disminuida</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Se agrega SEVERAMENTE a la disminución de función, en descripción y conclusión</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>&lt;30%</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Función ventricular</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>FE 50-53% (límítrofe, corregido)</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Contractilidad global límítrofe</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Bug corregido: la descripción global seguía diciendo "conservada" aunque la conclusión ya decía límítrofe</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>50-53%</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral/aórtica/tricúspide</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>Grados con espacio (corregido)</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>IM 3 / IA 2 / IT 4 (con espacio antes del número)</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Bug corregido: el espacio entre la letra y el número de grado hacía que se ignorara silenciosamente, asumiendo "leve" por defecto sin avisar</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Riesgo clínico real: bajaba la severidad sin ningún aviso. Ahora funciona igual con o sin espacio</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales / Apertura</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Talla en metros (auto-detectado)</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Si la talla es &lt;3 (ej. "1,65"), se asume que está en metros y se convierte a cm automáticamente</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>&lt;3 → ×100</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Corrige cálculos absurdos de índice de masa VI cuando la talla se dicta en metros por costumbre</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Contractilidad</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>HPK GRAL</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Sinónimo de HPKGRAL/HPQ (hipoquinesia generalizada)</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>ANV ## [x##] [MOVIL/INMOVIL]</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Imagen ecodensa apical sugestiva de trombo (distinto de AN VI, que sigue siendo aneurisma)</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>"Imagen ecodensa localizada en ápex ventricular izquierdo de xx [x xx] cm de diámetro(s)[, móvil/no móvil]."</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Conclusión: "SUGIERE LA PRESENCIA DE TROMBO EN VENTRICULO IZQUIERDO."</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>AN VI (corregido)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Conversión mm→cm</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Bug corregido: no convertía mm a cm (mostraba "32 cm" en vez de "3.2 cm")</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades derechas</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Electrodo (conclusión actualizada)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Texto de conclusión revisado</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>"PRESENCIA DE ELECTRODOS DE ESTIMULACION INTRACAVITARIOS EN CAVIDADES DERECHAS." (antes: singular, sin "intracavitarios")</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>D?</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Sinónimo de DER? (flujos Doppler derechos no valorables)</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>EA ANILLO / EA+ANILLO</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Esclerosis de hojuelas + calcio en anillo, en una sola línea</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>"...esclerosis en sus hojuelas y calcio en su anillo valvular..."</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>"ESCLEROSIS Y LEVE CALCIFICACION VALVULAR AORTICA."</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Función ventricular</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>FEVI en blanco (confirmado)</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Si no se dicta FEVI (##%), se asume función conservada/normal salvo que se indique lo contrario</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Comportamiento confirmado con el usuario, no es un vacío</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>AN VI (corregido, definitivo)</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Dilatación aneurismática apical en VI — separado por completo de trombo</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>"Dilatación aneurismática apical en ventrículo izquierdo de ## cm de diámetro."</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>No relacionado con trombo/masas. Corrige mezcla conceptual previa (ANV eliminado)</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Masas y dispositivos</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>TX (totalmente flexible, definitivo)</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Trombo — medidas y localización ahora opcionales</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>TX solo → "Trombo en ápex del ventrículo izquierdo." TX con medidas y/o localización → las incluye. Localización por defecto: ápex del VI</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Ya no requiere formato "##x##" obligatorio como antes</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Masas y dispositivos</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>CAT / CATETER (separado, definitivo)</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Catéter — siempre genérico, igual patrón que electrodo</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>"Presencia de catéter en cavidades derechas." (ignora localización específica si se dicta)</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Conclusión: "PRESENCIA DE CATETER EN CAVIDADES DERECHAS."</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>E/A ##/## (ahora descrito)</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Onda E y onda A — bug corregido: se calculaba pero nunca se describía</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>"Onda E de ## cm/seg y onda A de ## cm/seg (relación E/A de #.##)."</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>CMP ## / CMP↓ ## (con valor)</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Grosor del calcio en velo posterior mitral</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>"...de ## cm de espesor..." agregado a la descripción existente</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Retrocompatible: CMP sin valor sigue funcionando</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades derechas</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>AD con guion/dos puntos</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>AD - ## / AD: ## ahora reconocidos</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Antes solo aceptaba espacio, no guion</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales / Apertura</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>MK (tolerado como KG)</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Error de tipeo frecuente de "KG"</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>El sistema acepta "MK" igual que "KG" para el peso</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>SENTADA / SENTADO</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Paciente en posición sentada</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>BCRI / BCRD</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Bloqueo completo de rama izquierda / derecha</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Van en CONDICION, no modifican el ritmo principal</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>BAV3 / BAV2 / MOBITZ I / MOBITZ II</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Bloqueos auriculoventriculares</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Van en CONDICION</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>BIGEMINISMO</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Bigeminismo en el momento del estudio</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Modifica la frase de apertura: "...RITMO [ritmo] CON BIGEMINISMO EN EL MOMENTO."</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>No es una condición más, se integra a la apertura</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>TT / T.T</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Paciente con toracostomía</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>4C / 4C: / 4C?</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>4C (sin ?) = estudio en cortes apicales (4 cámaras). 4C? = mala ventana apical</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Van en CONDICION</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>SX? / PE?</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Mala ventana subxifoidea / paraesternal</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Van en CONDICION</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Herramienta (motor)</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>Botón "Copiar al portapapeles" (corregido)</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Bug corregido: fallaba en silencio en algunos navegadores/contextos</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Ahora tiene método de respaldo automático y avisa explícitamente si ambos métodos fallan</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Afecta index.html, texto-continuo.html y motor-foto.html</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales / Apertura</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>Frecuencia cardiaca — SOLO dos formatos válidos (definitivo)</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>FC:## o ##/min, con o sin espacios</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Se eliminó por completo la detección posicional ("primer número suelto = FC")</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>IMPORTANTE: si no se dicta FC:## o ##/min explícitamente, el campo queda vacío — ya NO se infiere de la primera medida</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Función ventricular</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>Hipoquinesia generalizada por defecto (definitivo, sin "moderada")</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Cuando FEVI comprometida y NO hay alteraciones segmentarias dictadas</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>FE 50-53 (límítrofe) → "leve" hipoquinesia generalizada. FE 30-49 (disminuida) → "hipoquinesia generalizada" (SIN calificativo). FE &lt;30 → "severa" hipoquinesia generalizada</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Se integra en la misma línea que función sistólica. Un código OK explícito siempre anula esta regla</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>AI por diámetro (respaldo cuando no hay AI##)</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Clasificación de dilatación auricular izquierda cuando no se dictó código de área</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Diámetro ≥4.2 cm (de la secuencia fija de 7 medidas) → "Aurícula izquierda dilatada. Diámetro de ## cm." Si hay AI## (área), esta prevalece sobre el diámetro</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>≥4.2 cm</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Descripción de "normal" cambiada a "Aurícula izquierda de tamaño normal."</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral/aórtica</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>PVMM/PVMB (mitral) y PVAM/PVAB (aórtica) — corregido</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Prótesis valvular — ya no aparece contradictoriamente junto a "válvula normal"</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>La descripción de la válvula nativa se reemplaza por completo por la de la prótesis</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Ahora también aparece en CONCLUSIONES (antes faltaba por completo)</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>AVM ##,## (coma decimal corregida)</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Área valvular mitral por hemipresión — ahora se describe en Doppler independientemente de SM</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>"Área valvular mitral calculada por hemipresión de ## cm²."</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Antes solo aparecía si también había código SM (estenosis)</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral/aórtica/tricúspide</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>Grado T = trivial (nuevo)</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>IMT / IAT / ITT ahora reconocidos</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Se agrega "trivial" a la escala de grados existente (leve/leve-moderada/moderada/moderada-severa/severa)</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Antes "T" se ignoraba silenciosamente, quedando como "leve" por defecto</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Válvula tricúspide</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>Insuficiencia tricuspídea sin gradiente (bug corregido)</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Cualquier grado de IT ahora aparece en conclusiones aunque no se dicte Sxx</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>"INSUFICIENCIA VALVULAR TRICUSPIDEA [GRADO]." como línea independiente cuando no hay gradiente</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Bug importante: antes CUALQUIER grado de IT (no solo trivial) se perdía completamente de las conclusiones si faltaba el gradiente</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>M ##/ (definitivo)</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Gradiente pico de la onda E mitral</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>"Gradiente pico de la onda E mitral de ## mmHg."</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Formato exacto: M, espacio, número, barra al final. No confundir con M##% (variación respiratoria pericárdica) ni M solo (sexo)</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>AD - 19 (guion, definitivo)</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Área AD ahora tolera guion y dos puntos además de espacio</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5010,7 +7711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5389,8 +8090,92 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>FEVI límítrofe (50-53%) sin indicación explícita</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Si la FEVI está entre 50 y 53% inclusive, y no hay ningún código de alteración segmentaria ni el código OK dictado explícitamente, la contractilidad segmentaria se describe y concluye como "leve hipoquinesia generalizada" en vez de "normal". Si el médico dicta OK explícitamente, se respeta "normal" aunque la FEVI esté en ese rango.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Espacios opcionales en todos los códigos</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>El sistema es indiferente a los espacios entre el código y su valor: "S30", "S 30", "S-30" y "S:30" se interpretan igual. Aplica de forma general a todos los códigos del diccionario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Ecocardiograma normal: condición ampliada</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Nunca debe decir NORMAL si hay: FEVI reducida/límítrofe, insuficiencia tricuspídea, grasa pericárdica/epicárdica, derrame pleural, arritmias (ESV/EV/EXTRASIST), GRANULADO, hipertrofia de VD, remodelado geométrico, dilatación de raíz aórtica/AAA, hipertrofia de papilares. Se corrigieron múltiples vacíos donde estos hallazgos coexistían con "ECOCARDIOGRAMA NORMAL" erróneamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Calcificación de velo posterior mitral (CMP) no es conclusión independiente</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Se integra dentro de la única conclusión de la válvula mitral (agrega "CALCIFICACION" si no estaba ya mencionada por la morfología), nunca como línea aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Formato de datos cuantitativos alineado</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Se usan espacios fijos en vez de tabulaciones para garantizar alineación de columnas en cualquier visor/fuente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Gramática y/e</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>"y" se convierte en "e" antes de palabra que empieza con "i" (ej. "cm e inadecuado colapso").</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CONDICION: con mayúscula inicial</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>La línea de condición del encabezado siempre inicia con mayúscula.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B31"/>
+  <autoFilter ref="A1:B38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ORTIZNOR_Tabla_Maestra.xlsx
+++ b/ORTIZNOR_Tabla_Maestra.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7694,6 +7694,1079 @@
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>EM+ANILLO / EM ANILLO (nuevo, combinado)</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Esclerosis de hojuelas mitrales + calcio en anillo, en una sola línea</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>"...esclerosis en sus hojuelas y calcio en su anillo..."</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Si además hay código CMP, se integra automáticamente (calcio en velo posterior)</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr">
+        <is>
+          <t>AI##/## (volumen, definitivo)</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>El segundo número es SIEMPRE volumen total (no solo "volumen")</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>"...y volumen total de ## cc..." — unidad cambiada de ml a cc. Se indexa automáticamente cuando hay peso/talla: "(Volumen AI indexado ## cc/m²)"</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr">
+        <is>
+          <t>AVM (bug corregido, definitivo)</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Ya no aparece "null cm²" cuando no se dictó AVM</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Bug de inicialización: el valor por defecto era null (no undefined), y el chequeo no distinguía ambos casos</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Bug importante: aparecía en TODOS los pacientes sin AVM dictado, mostrando literalmente "...de null cm²."</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr">
+        <is>
+          <t>EXCAVADO</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Tórax excavado (pectus excavatum)</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Va en CONDICION</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Hipertensión pulmonar</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>S/S y S/SD fuerzan ALTA (definitivo)</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Sobrecarga sistólica o combinada del septum</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Refleja sobrecarga de PRESIÓN del VD (relevante para HP) — fuerza probabilidad ALTA directamente, incluso sin gradiente Sxx medido</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>S/D (diastólica pura, sobrecarga de volumen) NO fuerza alta por sí sola — sigue como criterio de apoyo únicamente</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Tabiques</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Aneurisma septal (AN, descripción y conclusión reescritas)</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Nueva frase descriptiva y diferenciación por estado del FOP</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: "Adelgazamiento aneurismático del septum interauricular en su tercio medio de ## x ## mm." Conclusión varía: sin FOP → "...SIN EVIDENCIA DE CORTOCIRCUITO"; con FOP dudoso (FOP?) → "...(PROBABLE FORAMEN OVAL PERMEABLE)"; con FOP confirmado → "...(ASOCIADO A FORAMEN OVAL PERMEABLE)"</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Antes decía genéricamente "(HALLAZGO ESTRUCTURAL ASOCIADO)", frase poco clara para otros médicos</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Válvula pulmonar</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>IP# integrado en conclusión de HP (definitivo)</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Regurgitación pulmonar ahora se combina con tricúspide en la línea de hipertensión pulmonar</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>IP solo → "REGURGITACION VALVULAR PULMONAR CON [prob] PARA HIPERTENSION PULMONAR." IP+tricúspide → "REGURGITACION VALVULAR PULMONAR Y TRICUSPIDEA CON..."</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Antes IP no aparecía en absoluto en la conclusión de HP</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Redacción general</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>Concordancia de género en "Jet" (corregido, definitivo)</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>"Jet" es masculino — los grados ahora concuerdan correctamente</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>"moderado"/"severo" en vez de "moderada"/"severa" específicamente en las frases de Doppler ("Jet de regurgitación... moderado")</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Las conclusiones ("INSUFICIENCIA VALVULAR... MODERADA") mantienen el género femenino correcto, ya que ahí concuerda con "insuficiencia"</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Hipertensión pulmonar</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>APEX BI/DER — duplicación corregida</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Ya no aparece "DILATACION DE CAVIDADES DERECHAS" dos veces en conclusiones</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Se eliminó la línea independiente redundante; queda integrada una sola vez dentro de la frase de hipertensión pulmonar</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>CM+ANILLO / CM ANILLO (nuevo, combinado)</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Esclerosis y calcificación de hojuelas + calcio en anillo, en una sola línea</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>"...esclerosis y calcificación en sus hojuelas y calcio en su anillo..."</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>SM — bug de contradicción corregido (definitivo)</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Descripción y conclusión ahora coinciden</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: "Válvula mitral con restricción de su apertura." (o integrado con morfo si coexiste). Ya no dice "excursionando adecuadamente" al mismo tiempo</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Además, ahora concluye "ESTENOSIS MITRAL." aunque no se dicte AVM (antes requería AVM obligatoriamente para generar la conclusión)</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>SM integrado con dilatación auricular izquierda</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Estenosis mitral + AI dilatada → una sola conclusión</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>"ESTENOSIS MITRAL [GRADO] (AVM ## CM²) CON DILATACION AURICULAR IZQUIERDA ASOCIADA."</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Tabiques</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>SEPTUM ↓↑ (orden inverso, definitivo)</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Ahora reconocido igual que SEPTUM ↑↓</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Masas y dispositivos</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>HUMO/CE/SMOK/SMOCK con localización VI por defecto</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Contraste espontáneo — localización explícita agregada</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>"Contraste espontáneo intracavitario en ventrículo izquierdo."</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Antes no mencionaba ninguna cavidad específica</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>VI dilatado por diámetro (respaldo automático, nuevo)</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Clasificación automática cuando no hay código explícito VI DIL/VI↑</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Diámetro diastólico (de la secuencia fija de 7 medidas) ≥5.7 cm → "Ventrículo izquierdo con diámetros aumentados, de morfología esferiforme." automáticamente</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>≥5.7 cm</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Mismo principio ya aplicado a la aurícula izquierda por diámetro</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>CA+ANILLO / CA ANILLO (nuevo, combinado)</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Esclerosis y calcificación de hojuelas aórticas + calcio en anillo, en una sola línea</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>"...esclerosis y calcificación en sus hojuelas y calcio en su anillo..."</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Análogo a EA+ANILLO</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral/aórtica</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Prótesis + insuficiencia (integradas, definitivo)</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Ya no aparece "NORMOFUNCIONANTE" y la insuficiencia por separado (contradictorio)</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>"PROTESIS VALVULAR [MITRAL/AORTICA] (código) CON INSUFICIENCIA [GRADO]." (una sola línea)</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Sin insuficiencia, sigue diciendo NORMOFUNCIONANTE</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Pericardio</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>PERICARDIO solo (bug corregido, definitivo)</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Ya no se pierde el derrame cuando no hay valor de espesor/volumen</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>"DERRAME PERICARDICO LEVE CON SIGNOS DE INFLAMACION PERICARDICA." (LEVE por defecto sin valor)</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Antes decía solo "INFLAMACION PERICARDICA" sin mencionar derrame</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Pericardio</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>DPP (bug de descripción corregido, definitivo)</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Ahora describe correctamente predominio posterior con el espesor</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>"Halo de ausencia de ecos de predominio posterior con ## cm de espesor."</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Antes el valor de DPP nunca se incluía en la descripción</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Contractilidad</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>SEGMENTARIA? (sinónimo de SEG?, definitivo)</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Función ventricular</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Función conservada + alteración segmentaria (frase corregida, definitivo)</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Ya no dice "conservada de origen isquémico" (contradictorio)</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>"FUNCION VENTRICULAR IZQUIERDA CONSERVADA CON ALTERACIONES SEGMENTARIAS QUE SUGIEREN SUSTRATO ISQUEMICO."</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>FE disminuida/severamente disminuida mantienen "DE ORIGEN ISQUEMICO" (sí aplica clínicamente)</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>SA (bug de contradicción corregido, definitivo)</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Ya no dice "apertura conservada" y "limitación para su apertura" a la vez</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>"Aórtica trivalva con limitación para su apertura y cierre central."</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Mismo patrón de corrección ya aplicado a SM (mitral)</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Gradiente aórtico movido a Doppler (definitivo)</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Ya no aparece en la sección de Válvulas</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>"Gradiente pico transvalvular aórtico de ## mmHg..." ahora en Doppler</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Estenosis + insuficiencia aórtica integradas (definitivo)</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Una sola conclusión en vez de dos líneas separadas</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>"[MORFOLOGIA] CON ESTENOSIS [GRADO] CON INSUFICIENCIA [GRADO]."</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Masas y dispositivos</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>Contraste espontáneo (CE/HUMO) reubicado (definitivo)</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Descripción movida a Cavidades/VI; conclusión integrada en función VI</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: dentro de "Ventrículo izquierdo...". Conclusión: sufijo "CON CONTRASTE ESPONTANEO INTRACAVITARIO" en la línea de función ventricular</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Ya no es hallazgo especial aparte ni conclusión independiente</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Contractilidad</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>DISINCRONIA (nuevo)</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Movimiento disincrónico septal — no es de origen isquémico, se describe aparte</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>"Movimiento disincrónico septal."</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>No activa la frase de "sustrato isquémico" (relacionado con conducción eléctrica, no isquemia)</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Hipertrofia VI + función sistólica integradas (definitivo)</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Una sola conclusión en vez de dos líneas separadas</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>"FUNCION SISTOLICA VENTRICULAR IZQUIERDA [ESTADO] CON HIPERTROFIA VENTRICULAR IZQUIERDA DE PATRON [CONCENTRICO/EXCENTRICO]."</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Se integra en las 4 variantes de la línea de función VI (conservada, isquémica, hipoquinesia, disminuida)</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>IOT (frase definitiva, reemplazo)</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Frase neutral de género, más completa</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>"Paciente en ventilación mecánica con intubación orotraqueal y en decúbito dorsal."</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Reemplaza la frase anterior por completo</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>IA EMI (sinónimo de IA ex mit, definitivo)</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Insuficiencia aórtica excéntrica hacia velo anterior mitral</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>"...excéntrico, hacia el velo anterior de la válvula mitral."</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>ORTIZNOR</t>
         </is>

--- a/ORTIZNOR_Tabla_Maestra.xlsx
+++ b/ORTIZNOR_Tabla_Maestra.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G224"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -8767,6 +8767,376 @@
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>PVAB (frase específica, sin código en texto)</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Prótesis biológica aórtica</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: "Prótesis biológica en posición aórtica con mecanismo oclusor funcionante." Conclusión: "PROTESIS VALVULAR AORTICA BIOLOGICA FUNCIONANTE." (o con insuficiencia si aplica)</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>PVAM sigue con formato genérico mostrando el código</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Masas y dispositivos</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>TX apical VI reubicado (definitivo)</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Cuando el trombo es apical del VI (por defecto o explícito), la descripción va en Cavidades/Ventrículo izquierdo, no en Hallazgos especiales</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>"Imagen ecodensa en ápex cardiaco que sugiere trombo de ## x ## mm." — la conclusión mantiene la misma prioridad alta de siempre</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Otras localizaciones (AD, AI, etc.) siguen en Hallazgos especiales</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>PM1/PM2/PM3 (severidad de prolapso, definitivo)</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>PM1 tiene frase específica; se integra con morfología en vez de reemplazarla</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>PM1: "rectificación leve de sus velos (sugestivo de prolapso leve)", integrado con esclerosis si coexiste. Conclusión combina morfología + prolapso + insuficiencia + dilatación AI en una sola línea</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>PM2/PM3 quedan genéricos ("prolapso de sus velos") por ahora</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Dilatación del VI en conclusiones (bug corregido, definitivo)</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>La dilatación ventricular (explícita o automática por diámetro) no generaba ninguna conclusión cuando no coincidía con patrón de hipertrofia</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Sufijo "CON DILATACION DEL VENTRICULO IZQUIERDO" agregado a las 4 variantes de la línea de función VI</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>No se duplica cuando ya está cubierto por hipertrofia excéntrica/remodelado excéntrico</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>CMP↓ (segunda corrección, definitiva)</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Bug recurrente de contradicción finalmente resuelto: ya no dice "excursionando adecuadamente" junto con "restricción de su excursión"</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>"Válvula mitral. Calcio en el velo posterior... con restricción de su excursión."</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Hipertensión pulmonar</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Límite de gradiente corregido: Sxx=40 (definitivo)</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>El valor exacto de 40 mmHg iba automáticamente a "baja probabilidad" sin considerar sobrecarga derecha</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Ahora Sxx=40 (no solo &gt;40) evalúa sobrecarga para escalar a alta/intermedia</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Umbral cambiado de ≤40 a &lt;40 para "baja" automática</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Herramienta (motor)</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr">
+        <is>
+          <t>Bug de parseo: cama con espacio interno (definitivo)</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>Camas como "603 A" hacían que el sistema interpretara la letra suelta como si fuera el nombre del paciente, perdiendo el nombre real</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>El mecanismo tolerante de "cama y nombre juntos" ahora exige que el texto capturado como nombre tenga al menos dos palabras (un nombre real), no una sola letra/sufijo de cama</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Bug real que causaba pérdida silenciosa del nombre del paciente</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>em↑ (nuevo, minúscula + flecha)</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Leve esclerosis CON engrosamiento — distinto de "em" (solo leve esclerosis) y "EM↑" (esclerosis y engrosamiento, sin "leve")</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>"leve esclerosis y engrosamiento en sus hojuelas"</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Ritmo / condiciones</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr">
+        <is>
+          <t>Extrasistolia fusionada con la apertura (definitivo)</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>ESV/EV/EXTRASIST ya no generan una conclusión independiente</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Se integran en la primera línea: "ESTUDIO ECOCARDIOGRAFICO REALIZADO EN RITMO [ritmo] CON FRECUENTE EXTRASISTOLIA [TIPO]." Se combina también con BIGEMINISMO si coexisten</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Mismo principio de fusión aplicado a lo largo de esta sesión</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>PM1/PM2/PM3 (escala final: leve/moderado/marcado)</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Simplificación de la severidad del prolapso mitral</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>PM1→"prolapso leve de sus velos"; PM2→"prolapso moderado de sus velos"; PM3→"prolapso marcado de sus velos" (mismo texto en descripción y conclusión, cambiando solo mayúsculas)</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Reemplaza la frase elaborada anterior de PM1 ("rectificación leve...") por esta versión más simple y uniforme</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>ORTIZNOR</t>
         </is>

--- a/ORTIZNOR_Tabla_Maestra.xlsx
+++ b/ORTIZNOR_Tabla_Maestra.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -9137,6 +9137,228 @@
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>IAEM (sinónimo de IA EMI)</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Insuficiencia aórtica excéntrica hacia velo anterior mitral</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>"...excéntrico, hacia el velo anterior de la válvula mitral."</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Antes se leía como IA central y el "EM" se descartaba sin aviso</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Tabiques/VI</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>SEPT VIBRADO / SEPTUM VIBRADO / SEP VIBR (bug corregido)</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Septum con movimiento vibrado</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>"Septum interventricular con movimiento vibrado."</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Antes SEPT/SEPTUM VIBRADO se leían como SEPTUM genérico y no escribían nada</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>E' ## / E´## / E’## (variantes de comilla) y E' SEP ##</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>e' lateral (y septal) por Doppler tisular</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>"Velocidad de la onda e' lateral basal por Doppler tisular de ## cm/seg." (septal: "septal basal")</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Antes E´ y E’ caían en no reconocidos, y con E' el valor se guardaba pero no se escribía</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>E/e' automático</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Cálculo de E/e' a partir del E de E/A y el e' lateral/septal (promedio si hay ambos)</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>"Relación E/e' de ## (calculada con e' lateral)." Un E/e dictado por el usuario tiene prioridad</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>E/e'&gt;14 positivo</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>También se escribe ahora el E/e dictado, que antes no aparecía. Regla de 2 criterios positivos sigue como "indeterminado" (pendiente de decisión)</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>AVA ##,## (coma decimal y ubicación)</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Área valvular aórtica por continuidad</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>"Área valvular aórtica calculada por continuidad de ## cm²." (ahora en Doppler)</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>AVA 1,2 se leía como 1 cm²</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Válvulas</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Morfología + ANILLO en una línea (EAB, CAB, EMB, CMB, EA.., EM.., CM.., con flecha)</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>El anillo ya no se pierde cuando se dicta en la misma línea que la morfología</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: "...Anillo valvular calcificado." Conclusión: "...LEVE CALCIO EN SU ANILLO."</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>EA/CA/EM/CM con +ANILLO conservan sus frases fusionadas propias</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>ORTIZNOR</t>
         </is>

--- a/ORTIZNOR_Tabla_Maestra.xlsx
+++ b/ORTIZNOR_Tabla_Maestra.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G240"/>
+  <dimension ref="A1:G254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -9359,6 +9359,524 @@
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Varios</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Variantes de escritura aceptadas (revisión de códigos no reconocidos)</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>PM 1 / PM 3 (espacio), 4C ? / 4 C?, SEGMENTRIA?, HK GENERAL / HPK GENERAL, HK - AS- M (espacios), EA .., M5/ (sin espacio), BIGEMINA, DIL, ANV ##, CM+ANILLO↑</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Se leen igual que sus códigos originales: PM1/PM3, 4C?, SEGMENTARIA?, hipoquinesia generalizada, HK-AS-M, EA.., M 5/, BIGEMINISMO, VI DIL, AN VI ##, CM↑ + anillo</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>ANV = AN VI (aneurisma apical). DIL = VI dilatado</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas / Tabiques</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>SEPTUM ## / SEPTIM ## y DIASTOLE ##</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Reemplazan el valor de la secuencia fija de 7 medidas</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>SEPTUM 12 → septum 1.2 cm. DIASTOLE 62 → diastólico VI 6.2 cm (activa dilatación VI si ≥5.7 cm). Enteros = mm; con decimal = cm</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Antes SEPTUM 12 se leía como "leve hipertrofia del septum" y el 12 se perdía sin aviso</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Condiciones</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>D.DERECHO / D DERECHO</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Decúbito derecho</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>CONDICION: Paciente en decúbito derecho</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Condiciones</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>TRAQUEOSTOMIA</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Traqueostomía (TX sigue siendo trombo)</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>CONDICION: Paciente con traqueostomía</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Condiciones</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>SX:</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Estudio en cortes subxifoideos (análogo a 4C:)</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>CONDICION: Estudio realizado en cortes subxifoideos</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>SX? sigue siendo mala ventana subxifoidea</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Pericardio</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>PERIC ##</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Pericardio inflamado con derrame (## ≥80 = cc; &lt;80 = cm)</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Descripción sin asumir predominio anterior. Conclusión: DERRAME PERICARDICO [severidad] ... CON SIGNOS DE INFLAMACION PERICARDICA</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>≤150 cc leve</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Masas y dispositivos</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>TX?</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Trombo dudoso en ápex del VI</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Descripción en VI: "Imagen ecodensa en ápex cardiaco que sugiere trombo". Conclusión: "SUGIERE LA PRESENCIA DE TROMBO EN VENTRICULO IZQUIERDO"</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>TX sin ? sigue siendo trombo definitivo</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Masas y dispositivos</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>ABSCESO ##X##</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Absceso perivalvular asociado a prótesis</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: "Imagen sugestiva de absceso perivalvular de ## x ## cm, asociada a prótesis valvular." Conclusión: "SUGIERE LA PRESENCIA DE ABSCESO PERIVALVULAR ASOCIADO A PROTESIS VALVULAR"</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Con decimales = cm; enteros = mm</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Masas y dispositivos</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>VEGETACION ##X## / EUSTACHIO</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Nombre completo de VEG y EUS</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Mismas frases que VEG y EUS</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Cavidades izquierdas</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>APENDICE ##/## / AURICULILLA ##X##</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Apéndice auricular (base y profundidad, en mm)</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>"Apéndice auricular libre, pequeño, con base de ## cm y profundidad ## cm, morfología en gorro de viento y libre de ecos."</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Estaba en el diccionario original pero nunca se había implementado</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>BIVALVA?</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Válvula aórtica probablemente bivalva</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: "Aórtica probablemente bivalva...". Conclusión: "VALVULA AORTICA PROBABLEMENTE BIVALVA" (integrada con el resto de la conclusión aórtica)</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Impide "ECOCARDIOGRAMA NORMAL"</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Válvula pulmonar</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>P ↑ ##</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Dilatación del tronco de la pulmonar</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>"Dilatación del tronco de la pulmonar con diámetro de ## cm." Conclusión: "DILATACION DEL TRONCO DE LA PULMONAR (## CM)"</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>No se incorpora a la probabilidad de HP</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>FEVI ##% y rangos con espacios o % (57 - 60%, 50%-48%)</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Fracción de eyección con etiqueta o rango</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Se leen como FE (ej. 57-60 %)</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Varios</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Códigos ignorados deliberadamente</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>EPSTEIN, FO, EMB ↑, T54/38, AA11</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Siguen apareciendo en "códigos no reconocidos" para revisión manual</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Decisión del médico</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
         <is>
           <t>ORTIZNOR</t>
         </is>

--- a/ORTIZNOR_Tabla_Maestra.xlsx
+++ b/ORTIZNOR_Tabla_Maestra.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G254"/>
+  <dimension ref="A1:G271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Conclusión incluye severidad y volumen: "DERRAME PERICARDICO [LEVE/MODERADO/SEVERO], CON VOLUMEN ESTIMADO DE ## CC."</t>
+          <t>Conclusión incluye severidad y volumen: "DERRAME PERICARDICO [LEVE/MODERADO/SEVERO], CON VOLUMEN ESTIMADO DE ## CC." Con inflamación (PERIC): "DERRAME PERICARDICO [LEVE/MODERADO/SEVERO] (## CC) CON SIGNOS DE INFLAMACION PERICARDICA."</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Descriptivo (fuera del algoritmo de grado)</t>
+          <t>Variable adicional: ≤70 ms indica presión de AI elevada</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Ya NO participa en el cálculo del grado de disfunción diastólica (algoritmo Nagueh 2016); queda como hallazgo puramente descriptivo</t>
+          <t>Participa en el algoritmo ASE 2025 como variable adicional y en el del anillo mitral (EM + ANILLO ↑). TRIV es sinónimo</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>&lt;10 cm/s = criterio positivo</t>
+          <t>Reducido: sin edad ≤7 cm/s; con edad &lt;10 (20-39), &lt;8 (40-65), &lt;7 (&gt;65)</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>ASE 2016 (Nagueh)</t>
+          <t>ASE 2025 (Nagueh)</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>&lt;7 cm/s = criterio positivo</t>
+          <t>Reducido: sin edad ≤6 cm/s; con edad &lt;7 (20-39), &lt;6 (40-65), &lt;6 (&gt;65)</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>ASE 2016 (Nagueh)</t>
+          <t>ASE 2025 (Nagueh)</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>S/S y S/SD fuerzan ALTA (definitivo)</t>
+          <t>S/S, S/SD y S/D fuerzan ALTA (definitivo)</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>S/D (diastólica pura, sobrecarga de volumen) NO fuerza alta por sí sola — sigue como criterio de apoyo únicamente</t>
+          <t>S/D (diastólica) TAMBIÉN fuerza ALTA desde la Decimocuarta Ronda (decisión del médico).</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>E/e'&gt;14 positivo</t>
+          <t>Aumentado: promedio ≥14, lateral ≥13, septal ≥15</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr">
@@ -9446,17 +9446,17 @@
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>D.DERECHO / D DERECHO</t>
+          <t>D DER / D DERECHO / D.DER / D.DERECHO</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Decúbito derecho</t>
+          <t>Decúbito lateral derecho</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>CONDICION: Paciente en decúbito derecho</t>
+          <t>CONDICION: Paciente en decúbito lateral derecho</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Descripción sin asumir predominio anterior. Conclusión: DERRAME PERICARDICO [severidad] ... CON SIGNOS DE INFLAMACION PERICARDICA</t>
+          <t>Descripción sin asumir predominio anterior. Conclusión: DERRAME PERICARDICO [severidad] (## CC) CON SIGNOS DE INFLAMACION PERICARDICA</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -9877,6 +9877,635 @@
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Válvulas</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>PVAM / PVAB / PVMM / PVMB (frase propia por tipo)</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Prótesis valvular: PV + A/M (aórtica/mitral) + M/B (mecánica/biológica)</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: "Prótesis [mecánica|biológica] en posición [aórtica|mitral] con mecanismo oclusor funcionante." Conclusión: "PROTESIS VALVULAR [AORTICA|MITRAL] [MECANICA|BIOLOGICA] FUNCIONANTE." (con insuficiencia: "...CON INSUFICIENCIA [grado].")</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Ya no se muestra el código entre paréntesis ni la palabra "normofuncionante". Con prótesis, los códigos de la válvula nativa (EM, EA...) se ignoran a propósito</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>Aviso "dictar sexo H/M" eliminado</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>El informe ya no incluye la advertencia sobre el sexo</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>"Índice de masa ventricular izquierda de ## g/m²." (sin paréntesis)</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Sin sexo no se clasifica hipertrofia por masa</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Hipertensión pulmonar</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>S/S, S/SD y S/D fuerzan ALTA (resumen)</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Cualquier rectificación septal fuerza probabilidad ALTA</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>ALTA PROBABILIDAD… CON SOBRECARGA [SISTOLICA | DIASTOLICA | SISTOLICA Y DIASTOLICA] DEL SEPTUM</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Aun con gradiente bajo (ej. S25). Reemplaza la regla anterior en que S/D no forzaba ALTA</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>H## / M## (ej. H65, M 65)</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Código mixto: sexo y edad</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Fija el sexo (clasificación por masa) y guarda la edad para los límites de e'; en ambulatorio imprime "EDAD: ##A"</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>2 o 3 dígitos, sin validar rango. H y M solos siguen siendo solo sexo. Una "M 25" sin % se leería como mujer de 25 años</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>SDP ##/##</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Onda S / onda D de venas pulmonares (cm/s)</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>"Flujo de venas pulmonares con onda S de ## cm/seg y onda D de ## cm/seg (relación S/D de #.##)."</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>≤0.67 = presión de AI elevada</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Variable adicional del algoritmo; con FE ≥50% un valor &gt;0.67 no es informativo. No usar S/D (es sobrecarga septal)</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>E/e' con apóstrofe (E/e' ##, E/E' ##, E´/e´ ##)</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Variantes de escritura de E/e ##</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Igual que E/e ##: "Relación E/e' de ##."</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>DD ## con espacio (DD 2)</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Grado dictado con espacio</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Igual que DD2</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>DD solo sigue siendo decúbito dorsal; DD seguido de un dígito no válido (DD 4) avisa como no reconocido</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>DT ## / TD ## (ahora descrito)</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Tiempo de desaceleración</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>"Tiempo de desaceleración de la onda E de ## ms."</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>No participa en el algoritmo ASE 2025</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Diástole / Doppler</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>TRIV ##</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Sinónimo de TRI ##</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Igual que TRI ##</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Válvula mitral</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>EM + ANILLO ↑ (con o sin espacios)</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Engrosamiento y calcificación del anillo mitral (calcificación significativa)</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Descripción: "…Engrosamiento y calcificación del anillo valvular mitral." Conclusión: "ESCLEROSIS VALVULAR MITRAL CON ENGROSAMIENTO Y CALCIFICACION DEL ANILLO MITRAL" (integra la insuficiencia si hay)</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>El algoritmo diastólico general no se aplica: se usa la Figura 4 de la guía (E/A y TRI). CM+ANILLO↑ conserva su significado (CM↑ + anillo)</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Función diastólica</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>FUNCION DIASTOLICA NORMAL</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Conclusión cuando la función diastólica es normal</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>"FUNCION DIASTOLICA NORMAL."</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>e' no reducido, E/e' normal y S## ≤31 mmHg</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Requiere e', E/e' calculable y S##. No coexiste con ECOCARDIOGRAMA NORMAL porque S## genera la línea de regurgitación tricuspídea</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Función diastólica</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>Presión de llenado elevada (anillo mitral)</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Resultado de la Figura 4 de la guía</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>"ELEVACION DE LA PRESION DE LLENADO DEL VENTRICULO IZQUIERDO"</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>E/A &gt;1.8, o E/A 0.8 a 1.8 con TRI &lt;80 ms</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Solo con EM + ANILLO ↑. Si es normal no se escribe nada</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Función diastólica</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Algoritmo ASE 2025 (resumen)</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Reemplaza al algoritmo de 2016</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Ver hoja "Algoritmo Diástole"</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Sin e' dictado no se concluye nada. e' por edad con H##/M##/EDAD:##</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr">
+        <is>
+          <t>Fracción de eyección: vale la última dictada</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Si se dicta más de una FE (ej. 65% y luego 69%)</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Se usa la última (formatos ##%, FE:## y FEVI ##)</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Un número suelto después de la FE no se toma como FE</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Función diastólica</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>Corte único S## = 31 mmHg (definitivo)</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Un solo corte de gradiente de IT para toda la función diastólica</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>IT aumentada si S## &gt;31 mmHg; función diastólica normal si S## ≤31 mmHg</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>31 mmHg ≈ 2.8 m/s</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Reemplaza el corte de 34 mmHg propuesto antes. S## de 31 exacto cuenta como normal</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Pericardio</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr">
+        <is>
+          <t>Derrame con inflamación: volumen entre paréntesis (definitivo)</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>DP/PERIC con volumen y signos de inflamación</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>"DERRAME PERICARDICO [LEVE/MODERADO/SEVERO] (## CC) CON SIGNOS DE INFLAMACION PERICARDICA."</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Leve ≤150 cc; moderado 151–300; severo &gt;300</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Evita dos "CON" seguidos. Sin inflamación se conserva "…, CON VOLUMEN ESTIMADO DE ## CC."; sin volumen no cambia</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>ORTIZNOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Datos generales</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>## AÑOS / EDAD ## (ej. 23 AÑOS, 23AÑOS, 23 años, EDAD 23)</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Edad sola, sin sexo</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Guarda la edad para los límites de e' (Tabla 6 ASE 2025); en modo ambulatorio imprime "EDAD: ##A"</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Acepta AÑO, AÑOS y ANOS, en mayúscula o minúscula. 2 o 3 dígitos, sin validar rango. No fija el sexo: para sexo y edad juntos usar H##/M##. EDAD:## con dos puntos ya existía</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>ORTIZNOR</t>
         </is>
@@ -10814,7 +11443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10842,153 +11471,255 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>0. Selección de rama</t>
+          <t>Fuente y alcance</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>El sistema decide automáticamente según la FEVI/SLG ya reportada en el mismo paciente</t>
+          <t>Guía ASE 2025: Nagueh SF et al. J Am Soc Echocardiogr 2025;38(7):537-569, doi:10.1016/j.echo.2025.03.011. Reemplaza el algoritmo ASE/EACVI 2016. Independiente de la FE.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>FEVI/SLG normal, sin enfermedad miocárdica → Rama 1. FEVI/SLG anormal o anomalía estructural → Rama 2</t>
+          <t>Figura 2 (diagnóstico) y Figura 3 (presión de AI y grado) de la guía</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Override manual</t>
+          <t>Exclusiones</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Si se dicta directamente DD1, DD2 o DD3</t>
+          <t>FA · prótesis mitral (PVMM/PVMB) · estenosis mitral (SM)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Ese valor tiene PRIORIDAD ABSOLUTA; el sistema no recalcula</t>
+          <t>No se concluye nada. No implementadas: insuficiencia mitral primaria severa, TEER, trasplante, HP no cardíaca, constricción pericárdica, asistencia ventricular</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RAMA 1 — criterios (FEVI/SLG normal)</t>
+          <t>Override manual</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>E/e' promedio &gt;14 · e' septal &lt;7cm/s · e' lateral &lt;10cm/s · Sxx &gt;31mmHg (equivale a Vel. IT &gt;2.8 m/s) · Volumen indexado de AI &gt;34 ml/m²</t>
+          <t>Si se dicta DD1, DD2 o DD3 (también con espacio: DD 2)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0-1 positivo → Normal · 2 positivos → Indeterminado · 3-4 positivos → Disfunción diastólica</t>
+          <t>Prioridad absoluta; el sistema no recalcula</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RAMA 2 — punto de partida</t>
+          <t>Anillo mitral calcificado (EM + ANILLO ↑)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Se evalúa E/A</t>
+          <t>Calcificación significativa del anillo mitral: el algoritmo general no se aplica; se usa la Figura 4 de la guía (solo E/A y TRI)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>E/A ≤0.8 + E ≤50 cm/s → Grado 1 (presión de AI normal)</t>
+          <t>E/A &lt;0.8 → presión de AI normal (no se escribe nada) · E/A &gt;1.8 → "ELEVACION DE LA PRESION DE LLENADO DEL VENTRICULO IZQUIERDO" · E/A 0.8 a 1.8 → TRI ≥80 ms normal (nada); TRI &lt;80 ms elevada; sin TRI nada</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RAMA 2 — zona intermedia</t>
+          <t>Punto de partida: e'</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>E/A ≤0.8 + E &gt;50 cm/s, o E/A 0.8 a &lt;2 → evaluar 3 criterios: E/e' promedio &gt;14 · Sxx &gt;31mmHg · Volumen indexado AI &gt;34 ml/m²</t>
+          <t>e' dictado (E'## lateral; E' SEP ## septal)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2-3 de 3 negativos → Grado 1 · 2-3 de 3 positivos → Grado 2. Con solo 2 criterios disponibles: 2 negativos→Grado1; 1 pos+1 neg→indeterminado; 2 positivos→Grado 2</t>
+          <t>Sin e' dictado no se concluye nada: la guía parte de e'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RAMA 2 — E/A alto</t>
+          <t>e' reducido</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>E/A ≥2</t>
+          <t>Con edad dictada (H65, M65, 65 AÑOS o EDAD:##), Tabla 6: 20-39 años septal &lt;7, lateral &lt;10, promedio &lt;9 · 40-65 años &lt;6, &lt;8, &lt;7 · &gt;65 años &lt;6, &lt;7, &lt;6.5. Sin edad: septal ≤6, lateral ≤7, promedio ≤6.5 (Figuras 2 y 3)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Grado 3 (presión de AI muy elevada)</t>
+          <t>Con edad se usa "&lt;" (Tabla 6); sin edad se usa "≤" (Figuras). La guía es inconsistente entre ambos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TRI</t>
+          <t>E/e'</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ya NO participa en el cálculo del grado</t>
+          <t>Dictado (E/e ##) o calculado: E (de E/A ##/##) ÷ e' (lateral; promedio si hay septal)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Queda solo como hallazgo descriptivo ("inversión de la relación E:A, con TRIV de xx ms")</t>
+          <t>Aumentado: promedio ≥14 · lateral ≥13 · septal ≥15</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>e' — convención de dictado</t>
+          <t>Velocidad de IT</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Sin sufijo = lateral (default); "E' sep" / "E' septal" = específico septal</t>
+          <t>S## (gradiente pico de IT, mmHg). Corte único: 31 mmHg</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Aumentada si S## &gt;31 mmHg (equivale a los 2.8 m/s de la guía). Con 31 exacto cuenta como normal</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Sxx como sustituto de velocidad IT</t>
+          <t>Figura 2 — ¿hay disfunción diastólica?</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sxx (gradiente pico sistólico en mmHg) &gt;31 mmHg</t>
+          <t>Marcadores: E/e' aumentado · E/A ≤0.8 o ≥2 · volumen indexado de AI &gt;34 ml/m²</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Equivale a velocidad de IT &gt;2.8 m/s (gradiente = 4V²)</t>
+          <t>e' reducido + ≥1 marcador → disfunción · e' no reducido + ≥2 marcadores → disfunción · en otro caso no hay disfunción</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Figura 3 — grado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Variables: e' reducido · E/e' aumentado · IT aumentada (S## &gt;31 mmHg)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Las 3 → grado 2 (E/A &lt;2) o grado 3 (E/A ≥2) · solo e' reducido con E/A ≤0.8 → grado 1 · casos intermedios → variable adicional</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Variables adicionales</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Volumen indexado de AI &gt;34 ml/m² · TRI ≤70 ms · SDP (S/D de venas pulmonares) ≤0.67</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Si alguna se cumple → presión de AI elevada → grado 2 o 3 según E/A · si ninguna lo indica y e' reducido con E/A ≤0.8 → grado 1 · sin variables adicionales → disfunción sin grado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SDP (venas pulmonares)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SDP ##/## = onda S / onda D en cm/s</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>≤0.67 siempre cuenta como positiva · &gt;0.67 cuenta como normal solo con FE &lt;50% (con FE normal no es informativa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Función diastólica normal</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Sin disfunción (Fig. 2) y e' no reducido y E/e' normal y S## ≤31 mmHg</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>"FUNCION DIASTOLICA NORMAL". Usa el mismo corte único de 31 mmHg que la IT aumentada (decisión del médico); S## de 31 exacto cuenta como normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Se describe siempre que se dicta: "inversión de la relación de ondas E:A, con TRI de ## ms" (TRI acompaña siempre a la inversión E/A). TRIV es sinónimo</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Participa como variable adicional (≤70 ms) y en el algoritmo del anillo mitral</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Interpretaciones del desarrollador</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>No literales en la guía: (1) con IT alta, un TRI &gt;70 ms se toma como variable adicional normal y permite el grado 1 · (2) las variables no dictadas se consideran no disponibles, no anormales · (3) la IT elevada no se discrimina en HP no cardíaca (Figura 6 no implementada)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Revisar con el médico si cambian los criterios</t>
         </is>
       </c>
     </row>
@@ -11685,12 +12416,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Integración entre función diastólica, presión de llenado y volumen de AI</t>
+          <t>Algoritmo de diagnóstico (Fig. 2), presión de AI y grado (Fig. 3), e' por edad (Tabla 6) y anillo mitral calcificado (Fig. 4)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ASE 2025</t>
+          <t>ASE 2025: Nagueh SF et al. J Am Soc Echocardiogr 2025;38(7):537-569. doi:10.1016/j.echo.2025.03.011 (reemplaza ASE/EACVI 2016)</t>
         </is>
       </c>
     </row>
